--- a/PBS_STRUKTUR_CANONICAL.xlsx
+++ b/PBS_STRUKTUR_CANONICAL.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Struktur PBS Kanonik" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Struktur PBS Kanonik'!$A$1:$G$199</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Struktur PBS Kanonik'!$A$1:$G$189</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -446,7 +446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G199"/>
+  <dimension ref="A1:G189"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -512,7 +512,7 @@
       <c r="D2" s="2" t="inlineStr"/>
       <c r="E2" s="2" t="inlineStr"/>
       <c r="F2" s="2" t="n">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="G2" s="2" t="inlineStr"/>
     </row>
@@ -759,7 +759,7 @@
       </c>
       <c r="E13" s="3" t="inlineStr"/>
       <c r="F13" s="3" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="G13" s="3" t="inlineStr"/>
     </row>
@@ -810,97 +810,97 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>1.3.3</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>3</v>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>Motor Screw Hopper Elektroda Tanur</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>5</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
         <is>
           <t>1.4</t>
         </is>
       </c>
-      <c r="B16" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="C16" s="3" t="inlineStr"/>
-      <c r="D16" s="4" t="inlineStr">
+      <c r="B17" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C17" s="3" t="inlineStr"/>
+      <c r="D17" s="4" t="inlineStr">
         <is>
           <t>Sistem Feeding / Charging</t>
         </is>
       </c>
-      <c r="E16" s="3" t="inlineStr"/>
-      <c r="F16" s="3" t="n">
+      <c r="E17" s="3" t="inlineStr"/>
+      <c r="F17" s="3" t="n">
         <v>24</v>
       </c>
-      <c r="G16" s="3" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="G17" s="3" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
         <is>
           <t>1.4.1</t>
         </is>
       </c>
-      <c r="B17" t="n">
-        <v>3</v>
-      </c>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" s="5" t="inlineStr">
+      <c r="B18" t="n">
+        <v>3</v>
+      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" s="5" t="inlineStr">
         <is>
           <t>Hoist Crane</t>
         </is>
       </c>
-      <c r="F17" t="n">
+      <c r="F18" t="n">
         <v>24</v>
       </c>
-      <c r="G17" t="n">
+      <c r="G18" t="n">
         <v>7</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="3" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
         <is>
           <t>1.5</t>
         </is>
       </c>
-      <c r="B18" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="C18" s="3" t="inlineStr"/>
-      <c r="D18" s="4" t="inlineStr">
+      <c r="B19" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C19" s="3" t="inlineStr"/>
+      <c r="D19" s="4" t="inlineStr">
         <is>
           <t>Sistem Daya Tanur</t>
         </is>
       </c>
-      <c r="E18" s="3" t="inlineStr"/>
-      <c r="F18" s="3" t="n">
+      <c r="E19" s="3" t="inlineStr"/>
+      <c r="F19" s="3" t="n">
         <v>63</v>
       </c>
-      <c r="G18" s="3" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>1.5.1</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>3</v>
-      </c>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" s="5" t="inlineStr">
-        <is>
-          <t>Trafo Step Down Tanur</t>
-        </is>
-      </c>
-      <c r="F19" t="n">
-        <v>23</v>
-      </c>
-      <c r="G19" t="n">
-        <v>8</v>
-      </c>
+      <c r="G19" s="3" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>1.5.2</t>
+          <t>1.5.1</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -910,20 +910,20 @@
       <c r="D20" t="inlineStr"/>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>Cubicle Sistem Daya Tanur</t>
+          <t>Trafo Step Down Tanur</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="G20" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>1.5.3</t>
+          <t>1.5.2</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -933,108 +933,108 @@
       <c r="D21" t="inlineStr"/>
       <c r="E21" s="5" t="inlineStr">
         <is>
+          <t>Cubicle Sistem Daya Tanur</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>18</v>
+      </c>
+      <c r="G21" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>1.5.3</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>3</v>
+      </c>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
           <t>Busbar / Bus Tube / Flexible Cable</t>
         </is>
       </c>
-      <c r="F21" t="n">
+      <c r="F22" t="n">
         <v>22</v>
       </c>
-      <c r="G21" t="n">
+      <c r="G22" t="n">
         <v>6</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="3" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
         <is>
           <t>1.6</t>
         </is>
       </c>
-      <c r="B22" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="C22" s="3" t="inlineStr"/>
-      <c r="D22" s="4" t="inlineStr">
+      <c r="B23" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C23" s="3" t="inlineStr"/>
+      <c r="D23" s="4" t="inlineStr">
         <is>
           <t>Sistem Kontrol dan Instrumentasi</t>
         </is>
       </c>
-      <c r="E22" s="3" t="inlineStr"/>
-      <c r="F22" s="3" t="n">
+      <c r="E23" s="3" t="inlineStr"/>
+      <c r="F23" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="G22" s="3" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
+      <c r="G23" s="3" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
         <is>
           <t>1.6.1</t>
         </is>
       </c>
-      <c r="B23" t="n">
-        <v>3</v>
-      </c>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" s="5" t="inlineStr">
+      <c r="B24" t="n">
+        <v>3</v>
+      </c>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" s="5" t="inlineStr">
         <is>
           <t>Panel Consule Control</t>
         </is>
       </c>
-      <c r="F23" t="n">
+      <c r="F24" t="n">
         <v>17</v>
       </c>
-      <c r="G23" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="3" t="inlineStr">
+      <c r="G24" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
         <is>
           <t>1.7</t>
         </is>
       </c>
-      <c r="B24" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="C24" s="3" t="inlineStr"/>
-      <c r="D24" s="4" t="inlineStr">
+      <c r="B25" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C25" s="3" t="inlineStr"/>
+      <c r="D25" s="4" t="inlineStr">
         <is>
           <t>Sistem Pendinginan Air</t>
         </is>
       </c>
-      <c r="E24" s="3" t="inlineStr"/>
-      <c r="F24" s="3" t="n">
+      <c r="E25" s="3" t="inlineStr"/>
+      <c r="F25" s="3" t="n">
         <v>24</v>
       </c>
-      <c r="G24" s="3" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>1.7.1</t>
-        </is>
-      </c>
-      <c r="B25" t="n">
-        <v>3</v>
-      </c>
-      <c r="C25" t="inlineStr"/>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" s="5" t="inlineStr">
-        <is>
-          <t>Water Jacket</t>
-        </is>
-      </c>
-      <c r="F25" t="n">
-        <v>5</v>
-      </c>
-      <c r="G25" t="n">
-        <v>0</v>
-      </c>
+      <c r="G25" s="3" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>1.7.2</t>
+          <t>1.7.1</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -1044,20 +1044,20 @@
       <c r="D26" t="inlineStr"/>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>Water Box</t>
+          <t>Water Jacket</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="G26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>1.7.3</t>
+          <t>1.7.2</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1067,64 +1067,64 @@
       <c r="D27" t="inlineStr"/>
       <c r="E27" s="5" t="inlineStr">
         <is>
+          <t>Water Box</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>13</v>
+      </c>
+      <c r="G27" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>1.7.3</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>3</v>
+      </c>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
           <t>Pompa sirkulasi</t>
         </is>
       </c>
-      <c r="F27" t="n">
+      <c r="F28" t="n">
         <v>6</v>
       </c>
-      <c r="G27" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="3" t="inlineStr">
+      <c r="G28" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
         <is>
           <t>1.8</t>
         </is>
       </c>
-      <c r="B28" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="C28" s="3" t="inlineStr"/>
-      <c r="D28" s="4" t="inlineStr">
+      <c r="B29" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C29" s="3" t="inlineStr"/>
+      <c r="D29" s="4" t="inlineStr">
         <is>
           <t>Sistem Udara Bertekanan dan Sirkulasi Udara</t>
         </is>
       </c>
-      <c r="E28" s="3" t="inlineStr"/>
-      <c r="F28" s="3" t="n">
+      <c r="E29" s="3" t="inlineStr"/>
+      <c r="F29" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="G28" s="3" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>1.8.1</t>
-        </is>
-      </c>
-      <c r="B29" t="n">
-        <v>3</v>
-      </c>
-      <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" s="5" t="inlineStr">
-        <is>
-          <t>Pneumatic system</t>
-        </is>
-      </c>
-      <c r="F29" t="n">
-        <v>14</v>
-      </c>
-      <c r="G29" t="n">
-        <v>3</v>
-      </c>
+      <c r="G29" s="3" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>1.8.2</t>
+          <t>1.8.1</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -1134,108 +1134,108 @@
       <c r="D30" t="inlineStr"/>
       <c r="E30" s="5" t="inlineStr">
         <is>
+          <t>Pneumatic system</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>14</v>
+      </c>
+      <c r="G30" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>1.8.2</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>3</v>
+      </c>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
           <t>Blower Tiup</t>
         </is>
       </c>
-      <c r="F30" t="n">
-        <v>1</v>
-      </c>
-      <c r="G30" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="3" t="inlineStr">
+      <c r="F31" t="n">
+        <v>1</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
         <is>
           <t>1.9</t>
         </is>
       </c>
-      <c r="B31" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="C31" s="3" t="inlineStr"/>
-      <c r="D31" s="4" t="inlineStr">
+      <c r="B32" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C32" s="3" t="inlineStr"/>
+      <c r="D32" s="4" t="inlineStr">
         <is>
           <t>Sistem Tapping Logam dan Slag</t>
         </is>
       </c>
-      <c r="E31" s="3" t="inlineStr"/>
-      <c r="F31" s="3" t="n">
+      <c r="E32" s="3" t="inlineStr"/>
+      <c r="F32" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="G31" s="3" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
+      <c r="G32" s="3" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
         <is>
           <t>1.9.2</t>
         </is>
       </c>
-      <c r="B32" t="n">
-        <v>3</v>
-      </c>
-      <c r="C32" t="inlineStr"/>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" s="5" t="inlineStr">
+      <c r="B33" t="n">
+        <v>3</v>
+      </c>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" s="5" t="inlineStr">
         <is>
           <t>Tapping Launder / Spout</t>
         </is>
       </c>
-      <c r="F32" t="n">
+      <c r="F33" t="n">
         <v>11</v>
       </c>
-      <c r="G32" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="3" t="inlineStr">
+      <c r="G33" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
         <is>
           <t>1.10</t>
         </is>
       </c>
-      <c r="B33" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="C33" s="3" t="inlineStr"/>
-      <c r="D33" s="4" t="inlineStr">
+      <c r="B34" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C34" s="3" t="inlineStr"/>
+      <c r="D34" s="4" t="inlineStr">
         <is>
           <t>Sistem Penanganan Logam dan Slag Cair</t>
         </is>
       </c>
-      <c r="E33" s="3" t="inlineStr"/>
-      <c r="F33" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="G33" s="3" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>1.10.1</t>
-        </is>
-      </c>
-      <c r="B34" t="n">
-        <v>3</v>
-      </c>
-      <c r="C34" t="inlineStr"/>
-      <c r="D34" t="inlineStr"/>
-      <c r="E34" s="5" t="inlineStr">
-        <is>
-          <t>Prisma Pot</t>
-        </is>
-      </c>
-      <c r="F34" t="n">
-        <v>1</v>
-      </c>
-      <c r="G34" t="n">
-        <v>0</v>
-      </c>
+      <c r="E34" s="3" t="inlineStr"/>
+      <c r="F34" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G34" s="3" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>1.10.2</t>
+          <t>1.10.1</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1245,85 +1245,85 @@
       <c r="D35" t="inlineStr"/>
       <c r="E35" s="5" t="inlineStr">
         <is>
+          <t>Prisma Pot</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>1</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>1.10.2</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>3</v>
+      </c>
+      <c r="C36" t="inlineStr"/>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" s="5" t="inlineStr">
+        <is>
           <t>Slag Caster</t>
         </is>
       </c>
-      <c r="F35" t="n">
-        <v>1</v>
-      </c>
-      <c r="G35" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
+      <c r="F36" t="n">
+        <v>1</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B36" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
+      <c r="B37" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
         <is>
           <t>Area Pemurnian</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr"/>
-      <c r="E36" s="2" t="inlineStr"/>
-      <c r="F36" s="2" t="n">
-        <v>249</v>
-      </c>
-      <c r="G36" s="2" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="3" t="inlineStr">
+      <c r="D37" s="2" t="inlineStr"/>
+      <c r="E37" s="2" t="inlineStr"/>
+      <c r="F37" s="2" t="n">
+        <v>335</v>
+      </c>
+      <c r="G37" s="2" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
         <is>
           <t>2.1</t>
         </is>
       </c>
-      <c r="B37" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="C37" s="3" t="inlineStr"/>
-      <c r="D37" s="4" t="inlineStr">
+      <c r="B38" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C38" s="3" t="inlineStr"/>
+      <c r="D38" s="4" t="inlineStr">
         <is>
           <t>Sistem Refining Pot, Pengadukan, dan Transfer Timah</t>
         </is>
       </c>
-      <c r="E37" s="3" t="inlineStr"/>
-      <c r="F37" s="3" t="n">
+      <c r="E38" s="3" t="inlineStr"/>
+      <c r="F38" s="3" t="n">
         <v>54</v>
       </c>
-      <c r="G37" s="3" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>2.1.1</t>
-        </is>
-      </c>
-      <c r="B38" t="n">
-        <v>3</v>
-      </c>
-      <c r="C38" t="inlineStr"/>
-      <c r="D38" t="inlineStr"/>
-      <c r="E38" s="5" t="inlineStr">
-        <is>
-          <t>Ketel</t>
-        </is>
-      </c>
-      <c r="F38" t="n">
-        <v>30</v>
-      </c>
-      <c r="G38" t="n">
-        <v>13</v>
-      </c>
+      <c r="G38" s="3" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2.1.3</t>
+          <t>2.1.1</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -1333,20 +1333,20 @@
       <c r="D39" t="inlineStr"/>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t>Dudukan Mixer Pot Refining</t>
+          <t>Ketel</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2.1.5</t>
+          <t>2.1.3</t>
         </is>
       </c>
       <c r="B40" t="n">
@@ -1356,20 +1356,20 @@
       <c r="D40" t="inlineStr"/>
       <c r="E40" s="5" t="inlineStr">
         <is>
-          <t>Pompa Timah</t>
+          <t>Dudukan Mixer Pot Refining</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="G40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2.1.6</t>
+          <t>2.1.5</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -1379,64 +1379,64 @@
       <c r="D41" t="inlineStr"/>
       <c r="E41" s="5" t="inlineStr">
         <is>
+          <t>Pompa Timah</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>20</v>
+      </c>
+      <c r="G41" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2.1.6</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>3</v>
+      </c>
+      <c r="C42" t="inlineStr"/>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" s="5" t="inlineStr">
+        <is>
           <t>Mixer / Agitator Pot Refining (motor, shaft, dan impeller)</t>
         </is>
       </c>
-      <c r="F41" t="n">
-        <v>3</v>
-      </c>
-      <c r="G41" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="3" t="inlineStr">
+      <c r="F42" t="n">
+        <v>3</v>
+      </c>
+      <c r="G42" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
         <is>
           <t>2.2</t>
         </is>
       </c>
-      <c r="B42" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="C42" s="3" t="inlineStr"/>
-      <c r="D42" s="4" t="inlineStr">
+      <c r="B43" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C43" s="3" t="inlineStr"/>
+      <c r="D43" s="4" t="inlineStr">
         <is>
           <t>Sistem Crystallizer</t>
         </is>
       </c>
-      <c r="E42" s="3" t="inlineStr"/>
-      <c r="F42" s="3" t="n">
+      <c r="E43" s="3" t="inlineStr"/>
+      <c r="F43" s="3" t="n">
         <v>27</v>
       </c>
-      <c r="G42" s="3" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>2.2.1</t>
-        </is>
-      </c>
-      <c r="B43" t="n">
-        <v>3</v>
-      </c>
-      <c r="C43" t="inlineStr"/>
-      <c r="D43" t="inlineStr"/>
-      <c r="E43" s="5" t="inlineStr">
-        <is>
-          <t>Pot Crystallizer</t>
-        </is>
-      </c>
-      <c r="F43" t="n">
-        <v>14</v>
-      </c>
-      <c r="G43" t="n">
-        <v>3</v>
-      </c>
+      <c r="G43" s="3" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2.2.2</t>
+          <t>2.2.1</t>
         </is>
       </c>
       <c r="B44" t="n">
@@ -1446,20 +1446,20 @@
       <c r="D44" t="inlineStr"/>
       <c r="E44" s="5" t="inlineStr">
         <is>
-          <t>Motor Gearbox Crystallizer</t>
+          <t>Pot Crystallizer</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2.2.3</t>
+          <t>2.2.2</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -1469,64 +1469,64 @@
       <c r="D45" t="inlineStr"/>
       <c r="E45" s="5" t="inlineStr">
         <is>
+          <t>Motor Gearbox Crystallizer</t>
+        </is>
+      </c>
+      <c r="F45" t="n">
+        <v>9</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2.2.3</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>3</v>
+      </c>
+      <c r="C46" t="inlineStr"/>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" s="5" t="inlineStr">
+        <is>
           <t>Motor Gearbox Screw Crystallizer</t>
         </is>
       </c>
-      <c r="F45" t="n">
+      <c r="F46" t="n">
         <v>4</v>
       </c>
-      <c r="G45" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="3" t="inlineStr">
+      <c r="G46" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
         <is>
           <t>2.3</t>
         </is>
       </c>
-      <c r="B46" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="C46" s="3" t="inlineStr"/>
-      <c r="D46" s="4" t="inlineStr">
+      <c r="B47" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C47" s="3" t="inlineStr"/>
+      <c r="D47" s="4" t="inlineStr">
         <is>
           <t>Sistem Casting dan Pembentukan Ingot</t>
         </is>
       </c>
-      <c r="E46" s="3" t="inlineStr"/>
-      <c r="F46" s="3" t="n">
+      <c r="E47" s="3" t="inlineStr"/>
+      <c r="F47" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="G46" s="3" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>2.3.1</t>
-        </is>
-      </c>
-      <c r="B47" t="n">
-        <v>3</v>
-      </c>
-      <c r="C47" t="inlineStr"/>
-      <c r="D47" t="inlineStr"/>
-      <c r="E47" s="5" t="inlineStr">
-        <is>
-          <t>Wadah Cetak Ingot</t>
-        </is>
-      </c>
-      <c r="F47" t="n">
-        <v>7</v>
-      </c>
-      <c r="G47" t="n">
-        <v>1</v>
-      </c>
+      <c r="G47" s="3" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2.3.5</t>
+          <t>2.3.1</t>
         </is>
       </c>
       <c r="B48" t="n">
@@ -1536,20 +1536,20 @@
       <c r="D48" t="inlineStr"/>
       <c r="E48" s="5" t="inlineStr">
         <is>
-          <t>Talang Casting</t>
+          <t>Wadah Cetak Ingot</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2.3.6</t>
+          <t>2.3.5</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -1559,64 +1559,64 @@
       <c r="D49" t="inlineStr"/>
       <c r="E49" s="5" t="inlineStr">
         <is>
+          <t>Talang Casting</t>
+        </is>
+      </c>
+      <c r="F49" t="n">
+        <v>3</v>
+      </c>
+      <c r="G49" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2.3.6</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>3</v>
+      </c>
+      <c r="C50" t="inlineStr"/>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" s="5" t="inlineStr">
+        <is>
           <t>Pot Casting / Holding Kettle</t>
         </is>
       </c>
-      <c r="F49" t="n">
+      <c r="F50" t="n">
         <v>9</v>
       </c>
-      <c r="G49" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="3" t="inlineStr">
+      <c r="G50" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr">
         <is>
           <t>2.4</t>
         </is>
       </c>
-      <c r="B50" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="C50" s="3" t="inlineStr"/>
-      <c r="D50" s="4" t="inlineStr">
+      <c r="B51" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C51" s="3" t="inlineStr"/>
+      <c r="D51" s="4" t="inlineStr">
         <is>
           <t>Sistem Pemanasan dan Burner</t>
         </is>
       </c>
-      <c r="E50" s="3" t="inlineStr"/>
-      <c r="F50" s="3" t="n">
+      <c r="E51" s="3" t="inlineStr"/>
+      <c r="F51" s="3" t="n">
         <v>43</v>
       </c>
-      <c r="G50" s="3" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>2.4.1</t>
-        </is>
-      </c>
-      <c r="B51" t="n">
-        <v>3</v>
-      </c>
-      <c r="C51" t="inlineStr"/>
-      <c r="D51" t="inlineStr"/>
-      <c r="E51" s="5" t="inlineStr">
-        <is>
-          <t>Electrical Burner – Refining</t>
-        </is>
-      </c>
-      <c r="F51" t="n">
-        <v>22</v>
-      </c>
-      <c r="G51" t="n">
-        <v>10</v>
-      </c>
+      <c r="G51" s="3" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2.4.2</t>
+          <t>2.4.1</t>
         </is>
       </c>
       <c r="B52" t="n">
@@ -1626,20 +1626,20 @@
       <c r="D52" t="inlineStr"/>
       <c r="E52" s="5" t="inlineStr">
         <is>
-          <t>Electrical Burner – Crystallizer</t>
+          <t>Electrical Burner – Refining</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="G52" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2.4.3</t>
+          <t>2.4.2</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -1649,64 +1649,64 @@
       <c r="D53" t="inlineStr"/>
       <c r="E53" s="5" t="inlineStr">
         <is>
+          <t>Electrical Burner – Crystallizer</t>
+        </is>
+      </c>
+      <c r="F53" t="n">
+        <v>7</v>
+      </c>
+      <c r="G53" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2.4.3</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>3</v>
+      </c>
+      <c r="C54" t="inlineStr"/>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" s="5" t="inlineStr">
+        <is>
           <t>Burner – Flame Oven</t>
         </is>
       </c>
-      <c r="F53" t="n">
+      <c r="F54" t="n">
         <v>14</v>
       </c>
-      <c r="G53" t="n">
+      <c r="G54" t="n">
         <v>7</v>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="3" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="3" t="inlineStr">
         <is>
           <t>2.5</t>
         </is>
       </c>
-      <c r="B54" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="C54" s="3" t="inlineStr"/>
-      <c r="D54" s="4" t="inlineStr">
+      <c r="B55" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C55" s="3" t="inlineStr"/>
+      <c r="D55" s="4" t="inlineStr">
         <is>
           <t>Sistem Gas Handling, Ventilasi, dan Dust Collection</t>
         </is>
       </c>
-      <c r="E54" s="3" t="inlineStr"/>
-      <c r="F54" s="3" t="n">
-        <v>26</v>
-      </c>
-      <c r="G54" s="3" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>2.5.4</t>
-        </is>
-      </c>
-      <c r="B55" t="n">
-        <v>3</v>
-      </c>
-      <c r="C55" t="inlineStr"/>
-      <c r="D55" t="inlineStr"/>
-      <c r="E55" s="5" t="inlineStr">
-        <is>
-          <t>Pneumatic System Refining</t>
-        </is>
-      </c>
-      <c r="F55" t="n">
-        <v>2</v>
-      </c>
-      <c r="G55" t="n">
-        <v>1</v>
-      </c>
+      <c r="E55" s="3" t="inlineStr"/>
+      <c r="F55" s="3" t="n">
+        <v>104</v>
+      </c>
+      <c r="G55" s="3" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2.5.5</t>
+          <t>2.5.4</t>
         </is>
       </c>
       <c r="B56" t="n">
@@ -1716,11 +1716,11 @@
       <c r="D56" t="inlineStr"/>
       <c r="E56" s="5" t="inlineStr">
         <is>
-          <t>Bag House Refining</t>
+          <t>Pneumatic System Refining</t>
         </is>
       </c>
       <c r="F56" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G56" t="n">
         <v>1</v>
@@ -1729,7 +1729,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2.5.6</t>
+          <t>2.5.5</t>
         </is>
       </c>
       <c r="B57" t="n">
@@ -1739,20 +1739,20 @@
       <c r="D57" t="inlineStr"/>
       <c r="E57" s="5" t="inlineStr">
         <is>
-          <t>Blower Hisap Bag House Refining</t>
+          <t>Bag House Refining</t>
         </is>
       </c>
       <c r="F57" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2.5.11</t>
+          <t>2.5.6</t>
         </is>
       </c>
       <c r="B58" t="n">
@@ -1762,7 +1762,7 @@
       <c r="D58" t="inlineStr"/>
       <c r="E58" s="5" t="inlineStr">
         <is>
-          <t>Bag House Flame Oven</t>
+          <t>Blower Hisap Bag House Refining</t>
         </is>
       </c>
       <c r="F58" t="n">
@@ -1775,7 +1775,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2.5.14</t>
+          <t>2.5.11</t>
         </is>
       </c>
       <c r="B59" t="n">
@@ -1785,11 +1785,11 @@
       <c r="D59" t="inlineStr"/>
       <c r="E59" s="5" t="inlineStr">
         <is>
-          <t>Hood dan Ducting Penangkap Fume</t>
+          <t>Bag House Flame Oven</t>
         </is>
       </c>
       <c r="F59" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
@@ -1798,7 +1798,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2.5.15</t>
+          <t>2.5.14</t>
         </is>
       </c>
       <c r="B60" t="n">
@@ -1808,11 +1808,11 @@
       <c r="D60" t="inlineStr"/>
       <c r="E60" s="5" t="inlineStr">
         <is>
-          <t>Stack / Cerobong</t>
+          <t>Hood dan Ducting Penangkap Fume</t>
         </is>
       </c>
       <c r="F60" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -1821,7 +1821,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2.5.16</t>
+          <t>2.5.15</t>
         </is>
       </c>
       <c r="B61" t="n">
@@ -1831,41 +1831,43 @@
       <c r="D61" t="inlineStr"/>
       <c r="E61" s="5" t="inlineStr">
         <is>
+          <t>Stack / Cerobong</t>
+        </is>
+      </c>
+      <c r="F61" t="n">
+        <v>7</v>
+      </c>
+      <c r="G61" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2.5.16</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>3</v>
+      </c>
+      <c r="C62" t="inlineStr"/>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" s="5" t="inlineStr">
+        <is>
           <t>Cyclone - Pemurnian</t>
         </is>
       </c>
-      <c r="F61" t="n">
-        <v>1</v>
-      </c>
-      <c r="G61" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="3" t="inlineStr">
-        <is>
-          <t>2.6</t>
-        </is>
-      </c>
-      <c r="B62" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="C62" s="3" t="inlineStr"/>
-      <c r="D62" s="4" t="inlineStr">
-        <is>
-          <t>Sistem Pendinginan Air</t>
-        </is>
-      </c>
-      <c r="E62" s="3" t="inlineStr"/>
-      <c r="F62" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="G62" s="3" t="inlineStr"/>
+      <c r="F62" t="n">
+        <v>1</v>
+      </c>
+      <c r="G62" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2.6.1</t>
+          <t>2.5.17</t>
         </is>
       </c>
       <c r="B63" t="n">
@@ -1875,20 +1877,20 @@
       <c r="D63" t="inlineStr"/>
       <c r="E63" s="5" t="inlineStr">
         <is>
-          <t>Pompa Air Pendingin Pot Casting</t>
+          <t>ID Fan</t>
         </is>
       </c>
       <c r="F63" t="n">
-        <v>1</v>
+        <v>34</v>
       </c>
       <c r="G63" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2.6.2</t>
+          <t>2.5.18</t>
         </is>
       </c>
       <c r="B64" t="n">
@@ -1898,43 +1900,41 @@
       <c r="D64" t="inlineStr"/>
       <c r="E64" s="5" t="inlineStr">
         <is>
-          <t>Tower Tandon Air – Refining/Casting</t>
+          <t>Exhaust Fan</t>
         </is>
       </c>
       <c r="F64" t="n">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="G64" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>2.6.3</t>
-        </is>
-      </c>
-      <c r="B65" t="n">
-        <v>3</v>
-      </c>
-      <c r="C65" t="inlineStr"/>
-      <c r="D65" t="inlineStr"/>
-      <c r="E65" s="5" t="inlineStr">
-        <is>
-          <t>Sirkulasi Air</t>
-        </is>
-      </c>
-      <c r="F65" t="n">
-        <v>1</v>
-      </c>
-      <c r="G65" t="n">
-        <v>0</v>
-      </c>
+      <c r="A65" s="3" t="inlineStr">
+        <is>
+          <t>2.6</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C65" s="3" t="inlineStr"/>
+      <c r="D65" s="4" t="inlineStr">
+        <is>
+          <t>Sistem Pendinginan Air</t>
+        </is>
+      </c>
+      <c r="E65" s="3" t="inlineStr"/>
+      <c r="F65" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="G65" s="3" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2.6.5</t>
+          <t>2.6.1</t>
         </is>
       </c>
       <c r="B66" t="n">
@@ -1944,41 +1944,43 @@
       <c r="D66" t="inlineStr"/>
       <c r="E66" s="5" t="inlineStr">
         <is>
-          <t>Mesin Pompa Air Pendingin Crystallizer &amp; Casting</t>
+          <t>Pompa Air Pendingin Pot Casting</t>
         </is>
       </c>
       <c r="F66" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="3" t="inlineStr">
-        <is>
-          <t>2.7</t>
-        </is>
-      </c>
-      <c r="B67" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="C67" s="3" t="inlineStr"/>
-      <c r="D67" s="4" t="inlineStr">
-        <is>
-          <t>Sistem Kelistrikan, Kontrol, Instrumentasi, dan Interlock</t>
-        </is>
-      </c>
-      <c r="E67" s="3" t="inlineStr"/>
-      <c r="F67" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="G67" s="3" t="inlineStr"/>
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2.6.2</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>3</v>
+      </c>
+      <c r="C67" t="inlineStr"/>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" s="5" t="inlineStr">
+        <is>
+          <t>Tower Tandon Air – Refining/Casting</t>
+        </is>
+      </c>
+      <c r="F67" t="n">
+        <v>8</v>
+      </c>
+      <c r="G67" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2.7.1</t>
+          <t>2.6.3</t>
         </is>
       </c>
       <c r="B68" t="n">
@@ -1988,20 +1990,20 @@
       <c r="D68" t="inlineStr"/>
       <c r="E68" s="5" t="inlineStr">
         <is>
-          <t>Panel Electrical Refining</t>
+          <t>Sirkulasi Air</t>
         </is>
       </c>
       <c r="F68" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="G68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2.7.2</t>
+          <t>2.6.5</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -2011,11 +2013,11 @@
       <c r="D69" t="inlineStr"/>
       <c r="E69" s="5" t="inlineStr">
         <is>
-          <t>Panel Thermocouple Pot Refining</t>
+          <t>Mesin Pompa Air Pendingin Crystallizer &amp; Casting</t>
         </is>
       </c>
       <c r="F69" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -2024,7 +2026,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2.7.3</t>
+          <t>2.6.6</t>
         </is>
       </c>
       <c r="B70" t="n">
@@ -2034,64 +2036,64 @@
       <c r="D70" t="inlineStr"/>
       <c r="E70" s="5" t="inlineStr">
         <is>
-          <t>Panel Electrical Crystallizer</t>
+          <t>Water Instalasi</t>
         </is>
       </c>
       <c r="F70" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="G70" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="3" t="inlineStr">
-        <is>
-          <t>2.8</t>
-        </is>
-      </c>
-      <c r="B71" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="C71" s="3" t="inlineStr"/>
-      <c r="D71" s="4" t="inlineStr">
-        <is>
-          <t>Sistem Pengangkatan, Platform, dan Akses</t>
-        </is>
-      </c>
-      <c r="E71" s="3" t="inlineStr"/>
-      <c r="F71" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="G71" s="3" t="inlineStr"/>
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2.6.7</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>3</v>
+      </c>
+      <c r="C71" t="inlineStr"/>
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" s="5" t="inlineStr">
+        <is>
+          <t>Water Circulation</t>
+        </is>
+      </c>
+      <c r="F71" t="n">
+        <v>6</v>
+      </c>
+      <c r="G71" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>2.8.1</t>
-        </is>
-      </c>
-      <c r="B72" t="n">
-        <v>3</v>
-      </c>
-      <c r="C72" t="inlineStr"/>
-      <c r="D72" t="inlineStr"/>
-      <c r="E72" s="5" t="inlineStr">
-        <is>
-          <t>Hoist Crane – Refining</t>
-        </is>
-      </c>
-      <c r="F72" t="n">
-        <v>6</v>
-      </c>
-      <c r="G72" t="n">
-        <v>2</v>
-      </c>
+      <c r="A72" s="3" t="inlineStr">
+        <is>
+          <t>2.7</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C72" s="3" t="inlineStr"/>
+      <c r="D72" s="4" t="inlineStr">
+        <is>
+          <t>Sistem Kelistrikan, Kontrol, Instrumentasi, dan Interlock</t>
+        </is>
+      </c>
+      <c r="E72" s="3" t="inlineStr"/>
+      <c r="F72" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="G72" s="3" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2.8.2</t>
+          <t>2.7.1</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -2101,11 +2103,11 @@
       <c r="D73" t="inlineStr"/>
       <c r="E73" s="5" t="inlineStr">
         <is>
-          <t>Lantai Atas Refining</t>
+          <t>Panel Electrical Refining</t>
         </is>
       </c>
       <c r="F73" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="G73" t="n">
         <v>1</v>
@@ -2114,7 +2116,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2.8.3</t>
+          <t>2.7.2</t>
         </is>
       </c>
       <c r="B74" t="n">
@@ -2124,20 +2126,20 @@
       <c r="D74" t="inlineStr"/>
       <c r="E74" s="5" t="inlineStr">
         <is>
-          <t>Hoist Crane – Crystallizer</t>
+          <t>Panel Thermocouple Pot Refining</t>
         </is>
       </c>
       <c r="F74" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2.8.4</t>
+          <t>2.7.3</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -2147,64 +2149,64 @@
       <c r="D75" t="inlineStr"/>
       <c r="E75" s="5" t="inlineStr">
         <is>
-          <t>Hoist Crane – Casting</t>
+          <t>Panel Electrical Crystallizer</t>
         </is>
       </c>
       <c r="F75" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="G75" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>2.8.7</t>
-        </is>
-      </c>
-      <c r="B76" t="n">
-        <v>3</v>
-      </c>
-      <c r="C76" t="inlineStr"/>
-      <c r="D76" t="inlineStr"/>
-      <c r="E76" s="5" t="inlineStr">
-        <is>
-          <t>Hoist Crane – Gudang Ingot</t>
-        </is>
-      </c>
-      <c r="F76" t="n">
-        <v>1</v>
-      </c>
-      <c r="G76" t="n">
-        <v>0</v>
-      </c>
+      <c r="A76" s="3" t="inlineStr">
+        <is>
+          <t>2.8</t>
+        </is>
+      </c>
+      <c r="B76" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C76" s="3" t="inlineStr"/>
+      <c r="D76" s="4" t="inlineStr">
+        <is>
+          <t>Sistem Pengangkatan, Platform, dan Akses</t>
+        </is>
+      </c>
+      <c r="E76" s="3" t="inlineStr"/>
+      <c r="F76" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="G76" s="3" t="inlineStr"/>
     </row>
     <row r="77">
-      <c r="A77" s="3" t="inlineStr">
-        <is>
-          <t>2.9</t>
-        </is>
-      </c>
-      <c r="B77" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="C77" s="3" t="inlineStr"/>
-      <c r="D77" s="4" t="inlineStr">
-        <is>
-          <t>Persiapan Komposisi / Bahan Tambahan</t>
-        </is>
-      </c>
-      <c r="E77" s="3" t="inlineStr"/>
-      <c r="F77" s="3" t="n">
-        <v>14</v>
-      </c>
-      <c r="G77" s="3" t="inlineStr"/>
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2.8.1</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>3</v>
+      </c>
+      <c r="C77" t="inlineStr"/>
+      <c r="D77" t="inlineStr"/>
+      <c r="E77" s="5" t="inlineStr">
+        <is>
+          <t>Hoist Crane – Refining</t>
+        </is>
+      </c>
+      <c r="F77" t="n">
+        <v>6</v>
+      </c>
+      <c r="G77" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2.9.1</t>
+          <t>2.8.2</t>
         </is>
       </c>
       <c r="B78" t="n">
@@ -2214,41 +2216,43 @@
       <c r="D78" t="inlineStr"/>
       <c r="E78" s="5" t="inlineStr">
         <is>
-          <t>Mixer</t>
+          <t>Lantai Atas Refining</t>
         </is>
       </c>
       <c r="F78" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="G78" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="3" t="inlineStr">
-        <is>
-          <t>2.10</t>
-        </is>
-      </c>
-      <c r="B79" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="C79" s="3" t="inlineStr"/>
-      <c r="D79" s="4" t="inlineStr">
-        <is>
-          <t>Persiapan Antrasit</t>
-        </is>
-      </c>
-      <c r="E79" s="3" t="inlineStr"/>
-      <c r="F79" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="G79" s="3" t="inlineStr"/>
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2.8.3</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>3</v>
+      </c>
+      <c r="C79" t="inlineStr"/>
+      <c r="D79" t="inlineStr"/>
+      <c r="E79" s="5" t="inlineStr">
+        <is>
+          <t>Hoist Crane – Crystallizer</t>
+        </is>
+      </c>
+      <c r="F79" t="n">
+        <v>5</v>
+      </c>
+      <c r="G79" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2.10.1</t>
+          <t>2.8.4</t>
         </is>
       </c>
       <c r="B80" t="n">
@@ -2258,108 +2262,108 @@
       <c r="D80" t="inlineStr"/>
       <c r="E80" s="5" t="inlineStr">
         <is>
-          <t>Mesin Crusher</t>
+          <t>Hoist Crane – Casting</t>
         </is>
       </c>
       <c r="F80" t="n">
+        <v>2</v>
+      </c>
+      <c r="G80" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2.8.7</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>3</v>
+      </c>
+      <c r="C81" t="inlineStr"/>
+      <c r="D81" t="inlineStr"/>
+      <c r="E81" s="5" t="inlineStr">
+        <is>
+          <t>Hoist Crane – Gudang Ingot</t>
+        </is>
+      </c>
+      <c r="F81" t="n">
+        <v>1</v>
+      </c>
+      <c r="G81" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="3" t="inlineStr">
+        <is>
+          <t>2.9</t>
+        </is>
+      </c>
+      <c r="B82" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C82" s="3" t="inlineStr"/>
+      <c r="D82" s="4" t="inlineStr">
+        <is>
+          <t>Persiapan Komposisi / Bahan Tambahan</t>
+        </is>
+      </c>
+      <c r="E82" s="3" t="inlineStr"/>
+      <c r="F82" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="G82" s="3" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2.9.1</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>3</v>
+      </c>
+      <c r="C83" t="inlineStr"/>
+      <c r="D83" t="inlineStr"/>
+      <c r="E83" s="5" t="inlineStr">
+        <is>
+          <t>Mixer</t>
+        </is>
+      </c>
+      <c r="F83" t="n">
+        <v>14</v>
+      </c>
+      <c r="G83" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="3" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="B84" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C84" s="3" t="inlineStr"/>
+      <c r="D84" s="4" t="inlineStr">
+        <is>
+          <t>Persiapan Antrasit</t>
+        </is>
+      </c>
+      <c r="E84" s="3" t="inlineStr"/>
+      <c r="F84" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="G80" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="3" t="inlineStr">
-        <is>
-          <t>2.12</t>
-        </is>
-      </c>
-      <c r="B81" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="C81" s="3" t="inlineStr"/>
-      <c r="D81" s="4" t="inlineStr">
-        <is>
-          <t>Sistem Flame Oven</t>
-        </is>
-      </c>
-      <c r="E81" s="3" t="inlineStr"/>
-      <c r="F81" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="G81" s="3" t="inlineStr"/>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>2.12.1</t>
-        </is>
-      </c>
-      <c r="B82" t="n">
-        <v>3</v>
-      </c>
-      <c r="C82" t="inlineStr"/>
-      <c r="D82" t="inlineStr"/>
-      <c r="E82" s="5" t="inlineStr">
-        <is>
-          <t>Tanur Flame Oven</t>
-        </is>
-      </c>
-      <c r="F82" t="n">
-        <v>8</v>
-      </c>
-      <c r="G82" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="3" t="inlineStr">
-        <is>
-          <t>2.13</t>
-        </is>
-      </c>
-      <c r="B83" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="C83" s="3" t="inlineStr"/>
-      <c r="D83" s="4" t="inlineStr">
-        <is>
-          <t>Gudang dan Penimbangan Ingot</t>
-        </is>
-      </c>
-      <c r="E83" s="3" t="inlineStr"/>
-      <c r="F83" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="G83" s="3" t="inlineStr"/>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>2.13.1</t>
-        </is>
-      </c>
-      <c r="B84" t="n">
-        <v>3</v>
-      </c>
-      <c r="C84" t="inlineStr"/>
-      <c r="D84" t="inlineStr"/>
-      <c r="E84" s="5" t="inlineStr">
-        <is>
-          <t>Timbangan Duduk</t>
-        </is>
-      </c>
-      <c r="F84" t="n">
-        <v>2</v>
-      </c>
-      <c r="G84" t="n">
-        <v>0</v>
-      </c>
+      <c r="G84" s="3" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2.13.2</t>
+          <t>2.10.1</t>
         </is>
       </c>
       <c r="B85" t="n">
@@ -2369,85 +2373,85 @@
       <c r="D85" t="inlineStr"/>
       <c r="E85" s="5" t="inlineStr">
         <is>
-          <t>Anak Timbangan</t>
+          <t>Mesin Crusher</t>
         </is>
       </c>
       <c r="F85" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B86" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C86" s="2" t="inlineStr">
-        <is>
-          <t>Utilitas Pabrik</t>
-        </is>
-      </c>
-      <c r="D86" s="2" t="inlineStr"/>
-      <c r="E86" s="2" t="inlineStr"/>
-      <c r="F86" s="2" t="n">
-        <v>107</v>
-      </c>
-      <c r="G86" s="2" t="inlineStr"/>
+      <c r="A86" s="3" t="inlineStr">
+        <is>
+          <t>2.12</t>
+        </is>
+      </c>
+      <c r="B86" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C86" s="3" t="inlineStr"/>
+      <c r="D86" s="4" t="inlineStr">
+        <is>
+          <t>Sistem Flame Oven</t>
+        </is>
+      </c>
+      <c r="E86" s="3" t="inlineStr"/>
+      <c r="F86" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="G86" s="3" t="inlineStr"/>
     </row>
     <row r="87">
-      <c r="A87" s="3" t="inlineStr">
-        <is>
-          <t>3.1</t>
-        </is>
-      </c>
-      <c r="B87" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="C87" s="3" t="inlineStr"/>
-      <c r="D87" s="4" t="inlineStr">
-        <is>
-          <t>Sistem Kelistrikan Utama dan Daya Cadangan</t>
-        </is>
-      </c>
-      <c r="E87" s="3" t="inlineStr"/>
-      <c r="F87" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="G87" s="3" t="inlineStr"/>
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2.12.1</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>3</v>
+      </c>
+      <c r="C87" t="inlineStr"/>
+      <c r="D87" t="inlineStr"/>
+      <c r="E87" s="5" t="inlineStr">
+        <is>
+          <t>Tanur Flame Oven</t>
+        </is>
+      </c>
+      <c r="F87" t="n">
+        <v>8</v>
+      </c>
+      <c r="G87" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>3.1.1</t>
-        </is>
-      </c>
-      <c r="B88" t="n">
-        <v>3</v>
-      </c>
-      <c r="C88" t="inlineStr"/>
-      <c r="D88" t="inlineStr"/>
-      <c r="E88" s="5" t="inlineStr">
-        <is>
-          <t>Kubikel Incoming PLN</t>
-        </is>
-      </c>
-      <c r="F88" t="n">
-        <v>9</v>
-      </c>
-      <c r="G88" t="n">
-        <v>3</v>
-      </c>
+      <c r="A88" s="3" t="inlineStr">
+        <is>
+          <t>2.13</t>
+        </is>
+      </c>
+      <c r="B88" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C88" s="3" t="inlineStr"/>
+      <c r="D88" s="4" t="inlineStr">
+        <is>
+          <t>Gudang dan Penimbangan Ingot</t>
+        </is>
+      </c>
+      <c r="E88" s="3" t="inlineStr"/>
+      <c r="F88" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="G88" s="3" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>3.1.2</t>
+          <t>2.13.1</t>
         </is>
       </c>
       <c r="B89" t="n">
@@ -2457,20 +2461,20 @@
       <c r="D89" t="inlineStr"/>
       <c r="E89" s="5" t="inlineStr">
         <is>
-          <t>Genset</t>
+          <t>Timbangan Duduk</t>
         </is>
       </c>
       <c r="F89" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="G89" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>3.1.3</t>
+          <t>2.13.2</t>
         </is>
       </c>
       <c r="B90" t="n">
@@ -2480,66 +2484,62 @@
       <c r="D90" t="inlineStr"/>
       <c r="E90" s="5" t="inlineStr">
         <is>
-          <t>Panel Kubikel dan DSI</t>
+          <t>Anak Timbangan</t>
         </is>
       </c>
       <c r="F90" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>3.1.4</t>
-        </is>
-      </c>
-      <c r="B91" t="n">
-        <v>3</v>
-      </c>
-      <c r="C91" t="inlineStr"/>
-      <c r="D91" t="inlineStr"/>
-      <c r="E91" s="5" t="inlineStr">
-        <is>
-          <t>Panel Main Switch Board</t>
-        </is>
-      </c>
-      <c r="F91" t="n">
-        <v>2</v>
-      </c>
-      <c r="G91" t="n">
-        <v>1</v>
-      </c>
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>Utilitas Pabrik</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr"/>
+      <c r="E91" s="2" t="inlineStr"/>
+      <c r="F91" s="2" t="n">
+        <v>126</v>
+      </c>
+      <c r="G91" s="2" t="inlineStr"/>
     </row>
     <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>3.1.5</t>
-        </is>
-      </c>
-      <c r="B92" t="n">
-        <v>3</v>
-      </c>
-      <c r="C92" t="inlineStr"/>
-      <c r="D92" t="inlineStr"/>
-      <c r="E92" s="5" t="inlineStr">
-        <is>
-          <t>Panel Sinkron Genset</t>
-        </is>
-      </c>
-      <c r="F92" t="n">
-        <v>3</v>
-      </c>
-      <c r="G92" t="n">
-        <v>0</v>
-      </c>
+      <c r="A92" s="3" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="B92" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C92" s="3" t="inlineStr"/>
+      <c r="D92" s="4" t="inlineStr">
+        <is>
+          <t>Sistem Kelistrikan Utama dan Daya Cadangan</t>
+        </is>
+      </c>
+      <c r="E92" s="3" t="inlineStr"/>
+      <c r="F92" s="3" t="n">
+        <v>68</v>
+      </c>
+      <c r="G92" s="3" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>3.1.6</t>
+          <t>3.1.1</t>
         </is>
       </c>
       <c r="B93" t="n">
@@ -2549,20 +2549,20 @@
       <c r="D93" t="inlineStr"/>
       <c r="E93" s="5" t="inlineStr">
         <is>
-          <t>Panel Kapasitor Bank</t>
+          <t>Kubikel Incoming PLN</t>
         </is>
       </c>
       <c r="F93" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G93" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>3.1.7</t>
+          <t>3.1.2</t>
         </is>
       </c>
       <c r="B94" t="n">
@@ -2572,20 +2572,20 @@
       <c r="D94" t="inlineStr"/>
       <c r="E94" s="5" t="inlineStr">
         <is>
-          <t>Incoming Power Feeder</t>
+          <t>Genset</t>
         </is>
       </c>
       <c r="F94" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="G94" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>3.1.8</t>
+          <t>3.1.3</t>
         </is>
       </c>
       <c r="B95" t="n">
@@ -2595,41 +2595,43 @@
       <c r="D95" t="inlineStr"/>
       <c r="E95" s="5" t="inlineStr">
         <is>
-          <t>Main Power Transformer</t>
+          <t>Panel Kubikel dan DSI</t>
         </is>
       </c>
       <c r="F95" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="G95" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="3" t="inlineStr">
-        <is>
-          <t>3.2</t>
-        </is>
-      </c>
-      <c r="B96" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="C96" s="3" t="inlineStr"/>
-      <c r="D96" s="4" t="inlineStr">
-        <is>
-          <t>Sistem Udara Bertekanan Pabrik</t>
-        </is>
-      </c>
-      <c r="E96" s="3" t="inlineStr"/>
-      <c r="F96" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="G96" s="3" t="inlineStr"/>
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>3.1.4</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>3</v>
+      </c>
+      <c r="C96" t="inlineStr"/>
+      <c r="D96" t="inlineStr"/>
+      <c r="E96" s="5" t="inlineStr">
+        <is>
+          <t>Panel Main Switch Board</t>
+        </is>
+      </c>
+      <c r="F96" t="n">
+        <v>2</v>
+      </c>
+      <c r="G96" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>3.2.1</t>
+          <t>3.1.5</t>
         </is>
       </c>
       <c r="B97" t="n">
@@ -2639,20 +2641,20 @@
       <c r="D97" t="inlineStr"/>
       <c r="E97" s="5" t="inlineStr">
         <is>
-          <t>Kompresor Listrik</t>
+          <t>Panel Sinkron Genset</t>
         </is>
       </c>
       <c r="F97" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="G97" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>3.2.2</t>
+          <t>3.1.6</t>
         </is>
       </c>
       <c r="B98" t="n">
@@ -2662,41 +2664,43 @@
       <c r="D98" t="inlineStr"/>
       <c r="E98" s="5" t="inlineStr">
         <is>
-          <t>Tangki Kompresor</t>
+          <t>Panel Kapasitor Bank</t>
         </is>
       </c>
       <c r="F98" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G98" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="3" t="inlineStr">
-        <is>
-          <t>3.3</t>
-        </is>
-      </c>
-      <c r="B99" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="C99" s="3" t="inlineStr"/>
-      <c r="D99" s="4" t="inlineStr">
-        <is>
-          <t>Mesin Perkakas</t>
-        </is>
-      </c>
-      <c r="E99" s="3" t="inlineStr"/>
-      <c r="F99" s="3" t="n">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>3.1.7</t>
+        </is>
+      </c>
+      <c r="B99" t="n">
+        <v>3</v>
+      </c>
+      <c r="C99" t="inlineStr"/>
+      <c r="D99" t="inlineStr"/>
+      <c r="E99" s="5" t="inlineStr">
+        <is>
+          <t>Incoming Power Feeder</t>
+        </is>
+      </c>
+      <c r="F99" t="n">
         <v>4</v>
       </c>
-      <c r="G99" s="3" t="inlineStr"/>
+      <c r="G99" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>3.3.2</t>
+          <t>3.1.8</t>
         </is>
       </c>
       <c r="B100" t="n">
@@ -2706,20 +2710,20 @@
       <c r="D100" t="inlineStr"/>
       <c r="E100" s="5" t="inlineStr">
         <is>
-          <t>Mesin Milling</t>
+          <t>Main Power Transformer</t>
         </is>
       </c>
       <c r="F100" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="G100" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>3.3.6</t>
+          <t>3.1.11</t>
         </is>
       </c>
       <c r="B101" t="n">
@@ -2729,41 +2733,43 @@
       <c r="D101" t="inlineStr"/>
       <c r="E101" s="5" t="inlineStr">
         <is>
-          <t>Mesin Potong</t>
+          <t>Panel Battery</t>
         </is>
       </c>
       <c r="F101" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G101" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="3" t="inlineStr">
-        <is>
-          <t>3.4</t>
-        </is>
-      </c>
-      <c r="B102" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="C102" s="3" t="inlineStr"/>
-      <c r="D102" s="4" t="inlineStr">
-        <is>
-          <t>Sistem Bahan Bakar</t>
-        </is>
-      </c>
-      <c r="E102" s="3" t="inlineStr"/>
-      <c r="F102" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="G102" s="3" t="inlineStr"/>
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>3.1.12</t>
+        </is>
+      </c>
+      <c r="B102" t="n">
+        <v>3</v>
+      </c>
+      <c r="C102" t="inlineStr"/>
+      <c r="D102" t="inlineStr"/>
+      <c r="E102" s="5" t="inlineStr">
+        <is>
+          <t>Panel Furnace Tegangan Rendah</t>
+        </is>
+      </c>
+      <c r="F102" t="n">
+        <v>2</v>
+      </c>
+      <c r="G102" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>3.4.1</t>
+          <t>3.1.13</t>
         </is>
       </c>
       <c r="B103" t="n">
@@ -2773,7 +2779,7 @@
       <c r="D103" t="inlineStr"/>
       <c r="E103" s="5" t="inlineStr">
         <is>
-          <t>Pompa BBM</t>
+          <t>Distribution Board</t>
         </is>
       </c>
       <c r="F103" t="n">
@@ -2786,7 +2792,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>3.4.3</t>
+          <t>3.1.14</t>
         </is>
       </c>
       <c r="B104" t="n">
@@ -2796,64 +2802,64 @@
       <c r="D104" t="inlineStr"/>
       <c r="E104" s="5" t="inlineStr">
         <is>
-          <t>Tangki BBM</t>
+          <t>Trafo Step Up 20 kV</t>
         </is>
       </c>
       <c r="F104" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="G104" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="3" t="inlineStr">
-        <is>
-          <t>3.5</t>
-        </is>
-      </c>
-      <c r="B105" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="C105" s="3" t="inlineStr"/>
-      <c r="D105" s="4" t="inlineStr">
-        <is>
-          <t>Peralatan Pemindah Material</t>
-        </is>
-      </c>
-      <c r="E105" s="3" t="inlineStr"/>
-      <c r="F105" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="G105" s="3" t="inlineStr"/>
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>3.1.15</t>
+        </is>
+      </c>
+      <c r="B105" t="n">
+        <v>3</v>
+      </c>
+      <c r="C105" t="inlineStr"/>
+      <c r="D105" t="inlineStr"/>
+      <c r="E105" s="5" t="inlineStr">
+        <is>
+          <t>Ruang Trafo</t>
+        </is>
+      </c>
+      <c r="F105" t="n">
+        <v>1</v>
+      </c>
+      <c r="G105" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>3.5.1</t>
-        </is>
-      </c>
-      <c r="B106" t="n">
-        <v>3</v>
-      </c>
-      <c r="C106" t="inlineStr"/>
-      <c r="D106" t="inlineStr"/>
-      <c r="E106" s="5" t="inlineStr">
-        <is>
-          <t>Forklift</t>
-        </is>
-      </c>
-      <c r="F106" t="n">
-        <v>6</v>
-      </c>
-      <c r="G106" t="n">
-        <v>0</v>
-      </c>
+      <c r="A106" s="3" t="inlineStr">
+        <is>
+          <t>3.2</t>
+        </is>
+      </c>
+      <c r="B106" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C106" s="3" t="inlineStr"/>
+      <c r="D106" s="4" t="inlineStr">
+        <is>
+          <t>Sistem Udara Bertekanan Pabrik</t>
+        </is>
+      </c>
+      <c r="E106" s="3" t="inlineStr"/>
+      <c r="F106" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="G106" s="3" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>3.5.2</t>
+          <t>3.2.1</t>
         </is>
       </c>
       <c r="B107" t="n">
@@ -2863,41 +2869,43 @@
       <c r="D107" t="inlineStr"/>
       <c r="E107" s="5" t="inlineStr">
         <is>
-          <t>Conveyor</t>
+          <t>Kompresor Listrik</t>
         </is>
       </c>
       <c r="F107" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G107" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="3" t="inlineStr">
-        <is>
-          <t>3.6</t>
-        </is>
-      </c>
-      <c r="B108" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="C108" s="3" t="inlineStr"/>
-      <c r="D108" s="4" t="inlineStr">
-        <is>
-          <t>Struktur Sipil</t>
-        </is>
-      </c>
-      <c r="E108" s="3" t="inlineStr"/>
-      <c r="F108" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="G108" s="3" t="inlineStr"/>
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>3.2.2</t>
+        </is>
+      </c>
+      <c r="B108" t="n">
+        <v>3</v>
+      </c>
+      <c r="C108" t="inlineStr"/>
+      <c r="D108" t="inlineStr"/>
+      <c r="E108" s="5" t="inlineStr">
+        <is>
+          <t>Tangki Kompresor</t>
+        </is>
+      </c>
+      <c r="F108" t="n">
+        <v>6</v>
+      </c>
+      <c r="G108" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>3.6.1</t>
+          <t>3.2.3</t>
         </is>
       </c>
       <c r="B109" t="n">
@@ -2907,41 +2915,43 @@
       <c r="D109" t="inlineStr"/>
       <c r="E109" s="5" t="inlineStr">
         <is>
-          <t>Platform kerja</t>
+          <t>Jockey Pump</t>
         </is>
       </c>
       <c r="F109" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G109" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="3" t="inlineStr">
-        <is>
-          <t>3.7</t>
-        </is>
-      </c>
-      <c r="B110" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="C110" s="3" t="inlineStr"/>
-      <c r="D110" s="4" t="inlineStr">
-        <is>
-          <t>Sistem Proteksi Kebakaran</t>
-        </is>
-      </c>
-      <c r="E110" s="3" t="inlineStr"/>
-      <c r="F110" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="G110" s="3" t="inlineStr"/>
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>3.2.4</t>
+        </is>
+      </c>
+      <c r="B110" t="n">
+        <v>3</v>
+      </c>
+      <c r="C110" t="inlineStr"/>
+      <c r="D110" t="inlineStr"/>
+      <c r="E110" s="5" t="inlineStr">
+        <is>
+          <t>Mesin Compressor Sullair</t>
+        </is>
+      </c>
+      <c r="F110" t="n">
+        <v>2</v>
+      </c>
+      <c r="G110" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>3.7.1</t>
+          <t>3.2.5</t>
         </is>
       </c>
       <c r="B111" t="n">
@@ -2951,20 +2961,20 @@
       <c r="D111" t="inlineStr"/>
       <c r="E111" s="5" t="inlineStr">
         <is>
-          <t>Pompa Hydrant / Fire Pump</t>
+          <t>Pneumatic System</t>
         </is>
       </c>
       <c r="F111" t="n">
         <v>2</v>
       </c>
       <c r="G111" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="3" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>3.3</t>
         </is>
       </c>
       <c r="B112" s="3" t="n">
@@ -2973,19 +2983,19 @@
       <c r="C112" s="3" t="inlineStr"/>
       <c r="D112" s="4" t="inlineStr">
         <is>
-          <t>Perkakas dan Alat Ukur Workshop</t>
+          <t>Mesin Perkakas</t>
         </is>
       </c>
       <c r="E112" s="3" t="inlineStr"/>
       <c r="F112" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G112" s="3" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>3.8.2</t>
+          <t>3.3.2</t>
         </is>
       </c>
       <c r="B113" t="n">
@@ -2995,41 +3005,43 @@
       <c r="D113" t="inlineStr"/>
       <c r="E113" s="5" t="inlineStr">
         <is>
-          <t>Alat Ukur Maintenance / Peralatan Kelistrikan Workshop</t>
+          <t>Mesin Milling</t>
         </is>
       </c>
       <c r="F113" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G113" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B114" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C114" s="2" t="inlineStr">
-        <is>
-          <t>Area Peleburan Sekunder / Dust Recovery</t>
-        </is>
-      </c>
-      <c r="D114" s="2" t="inlineStr"/>
-      <c r="E114" s="2" t="inlineStr"/>
-      <c r="F114" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="G114" s="2" t="inlineStr"/>
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>3.3.6</t>
+        </is>
+      </c>
+      <c r="B114" t="n">
+        <v>3</v>
+      </c>
+      <c r="C114" t="inlineStr"/>
+      <c r="D114" t="inlineStr"/>
+      <c r="E114" s="5" t="inlineStr">
+        <is>
+          <t>Mesin Potong</t>
+        </is>
+      </c>
+      <c r="F114" t="n">
+        <v>1</v>
+      </c>
+      <c r="G114" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="3" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>3.4</t>
         </is>
       </c>
       <c r="B115" s="3" t="n">
@@ -3038,19 +3050,19 @@
       <c r="C115" s="3" t="inlineStr"/>
       <c r="D115" s="4" t="inlineStr">
         <is>
-          <t>Sistem Penerimaan, Penyimpanan, dan Pelletizing</t>
+          <t>Sistem Bahan Bakar</t>
         </is>
       </c>
       <c r="E115" s="3" t="inlineStr"/>
       <c r="F115" s="3" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="G115" s="3" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>4.1.3</t>
+          <t>3.4.1</t>
         </is>
       </c>
       <c r="B116" t="n">
@@ -3060,85 +3072,87 @@
       <c r="D116" t="inlineStr"/>
       <c r="E116" s="5" t="inlineStr">
         <is>
-          <t>Pelletizer</t>
+          <t>Pompa BBM</t>
         </is>
       </c>
       <c r="F116" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G116" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="3" t="inlineStr">
-        <is>
-          <t>4.2</t>
-        </is>
-      </c>
-      <c r="B117" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="C117" s="3" t="inlineStr"/>
-      <c r="D117" s="4" t="inlineStr">
-        <is>
-          <t>Rotary Kiln</t>
-        </is>
-      </c>
-      <c r="E117" s="3" t="inlineStr"/>
-      <c r="F117" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G117" s="3" t="inlineStr"/>
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>3.4.3</t>
+        </is>
+      </c>
+      <c r="B117" t="n">
+        <v>3</v>
+      </c>
+      <c r="C117" t="inlineStr"/>
+      <c r="D117" t="inlineStr"/>
+      <c r="E117" s="5" t="inlineStr">
+        <is>
+          <t>Tangki BBM</t>
+        </is>
+      </c>
+      <c r="F117" t="n">
+        <v>14</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>4.2.2</t>
-        </is>
-      </c>
-      <c r="B118" t="n">
-        <v>3</v>
-      </c>
-      <c r="C118" t="inlineStr"/>
-      <c r="D118" t="inlineStr"/>
-      <c r="E118" s="5" t="inlineStr">
-        <is>
-          <t>Burner – Rotary Kiln</t>
-        </is>
-      </c>
-      <c r="F118" t="n">
-        <v>1</v>
-      </c>
-      <c r="G118" t="n">
-        <v>0</v>
-      </c>
+      <c r="A118" s="3" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="B118" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C118" s="3" t="inlineStr"/>
+      <c r="D118" s="4" t="inlineStr">
+        <is>
+          <t>Peralatan Pemindah Material</t>
+        </is>
+      </c>
+      <c r="E118" s="3" t="inlineStr"/>
+      <c r="F118" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="G118" s="3" t="inlineStr"/>
     </row>
     <row r="119">
-      <c r="A119" s="3" t="inlineStr">
-        <is>
-          <t>4.3</t>
-        </is>
-      </c>
-      <c r="B119" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="C119" s="3" t="inlineStr"/>
-      <c r="D119" s="4" t="inlineStr">
-        <is>
-          <t>Sistem Flame Oven</t>
-        </is>
-      </c>
-      <c r="E119" s="3" t="inlineStr"/>
-      <c r="F119" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="G119" s="3" t="inlineStr"/>
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>3.5.1</t>
+        </is>
+      </c>
+      <c r="B119" t="n">
+        <v>3</v>
+      </c>
+      <c r="C119" t="inlineStr"/>
+      <c r="D119" t="inlineStr"/>
+      <c r="E119" s="5" t="inlineStr">
+        <is>
+          <t>Forklift</t>
+        </is>
+      </c>
+      <c r="F119" t="n">
+        <v>6</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>4.3.1</t>
+          <t>3.5.2</t>
         </is>
       </c>
       <c r="B120" t="n">
@@ -3148,20 +3162,20 @@
       <c r="D120" t="inlineStr"/>
       <c r="E120" s="5" t="inlineStr">
         <is>
-          <t>Tanur Flame Oven</t>
+          <t>Conveyor</t>
         </is>
       </c>
       <c r="F120" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G120" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="3" t="inlineStr">
         <is>
-          <t>4.4</t>
+          <t>3.6</t>
         </is>
       </c>
       <c r="B121" s="3" t="n">
@@ -3170,19 +3184,19 @@
       <c r="C121" s="3" t="inlineStr"/>
       <c r="D121" s="4" t="inlineStr">
         <is>
-          <t>Sistem Penanganan Gas Buang dan Debu</t>
+          <t>Struktur Sipil</t>
         </is>
       </c>
       <c r="E121" s="3" t="inlineStr"/>
       <c r="F121" s="3" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G121" s="3" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>4.4.1</t>
+          <t>3.6.1</t>
         </is>
       </c>
       <c r="B122" t="n">
@@ -3192,64 +3206,64 @@
       <c r="D122" t="inlineStr"/>
       <c r="E122" s="5" t="inlineStr">
         <is>
-          <t>Seattle Bawah Tanur</t>
+          <t>Platform kerja</t>
         </is>
       </c>
       <c r="F122" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G122" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>4.4.3</t>
-        </is>
-      </c>
-      <c r="B123" t="n">
-        <v>3</v>
-      </c>
-      <c r="C123" t="inlineStr"/>
-      <c r="D123" t="inlineStr"/>
-      <c r="E123" s="5" t="inlineStr">
-        <is>
-          <t>Dust Collector</t>
-        </is>
-      </c>
-      <c r="F123" t="n">
-        <v>4</v>
-      </c>
-      <c r="G123" t="n">
-        <v>0</v>
-      </c>
+      <c r="A123" s="3" t="inlineStr">
+        <is>
+          <t>3.7</t>
+        </is>
+      </c>
+      <c r="B123" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C123" s="3" t="inlineStr"/>
+      <c r="D123" s="4" t="inlineStr">
+        <is>
+          <t>Sistem Proteksi Kebakaran</t>
+        </is>
+      </c>
+      <c r="E123" s="3" t="inlineStr"/>
+      <c r="F123" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="G123" s="3" t="inlineStr"/>
     </row>
     <row r="124">
-      <c r="A124" s="3" t="inlineStr">
-        <is>
-          <t>4.5</t>
-        </is>
-      </c>
-      <c r="B124" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="C124" s="3" t="inlineStr"/>
-      <c r="D124" s="4" t="inlineStr">
-        <is>
-          <t>Sistem Kelistrikan, Kontrol, Instrumentasi, dan Interlock</t>
-        </is>
-      </c>
-      <c r="E124" s="3" t="inlineStr"/>
-      <c r="F124" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G124" s="3" t="inlineStr"/>
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>3.7.1</t>
+        </is>
+      </c>
+      <c r="B124" t="n">
+        <v>3</v>
+      </c>
+      <c r="C124" t="inlineStr"/>
+      <c r="D124" t="inlineStr"/>
+      <c r="E124" s="5" t="inlineStr">
+        <is>
+          <t>Pompa Hydrant / Fire Pump</t>
+        </is>
+      </c>
+      <c r="F124" t="n">
+        <v>2</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>4.5.1</t>
+          <t>3.7.2</t>
         </is>
       </c>
       <c r="B125" t="n">
@@ -3259,150 +3273,152 @@
       <c r="D125" t="inlineStr"/>
       <c r="E125" s="5" t="inlineStr">
         <is>
-          <t>Panel Electrical</t>
+          <t>Water / Hydrant</t>
         </is>
       </c>
       <c r="F125" t="n">
         <v>1</v>
       </c>
       <c r="G125" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B126" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C126" s="2" t="inlineStr">
-        <is>
-          <t>Area QC</t>
-        </is>
-      </c>
-      <c r="D126" s="2" t="inlineStr"/>
-      <c r="E126" s="2" t="inlineStr"/>
-      <c r="F126" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G126" s="2" t="inlineStr"/>
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>3.7.3</t>
+        </is>
+      </c>
+      <c r="B126" t="n">
+        <v>3</v>
+      </c>
+      <c r="C126" t="inlineStr"/>
+      <c r="D126" t="inlineStr"/>
+      <c r="E126" s="5" t="inlineStr">
+        <is>
+          <t>Motor Pump Hydrant</t>
+        </is>
+      </c>
+      <c r="F126" t="n">
+        <v>1</v>
+      </c>
+      <c r="G126" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="127">
-      <c r="A127" s="3" t="inlineStr">
-        <is>
-          <t>5.1</t>
-        </is>
-      </c>
-      <c r="B127" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="C127" s="3" t="inlineStr"/>
-      <c r="D127" s="4" t="inlineStr">
-        <is>
-          <t>Lab. Analisis</t>
-        </is>
-      </c>
-      <c r="E127" s="3" t="inlineStr"/>
-      <c r="F127" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G127" s="3" t="inlineStr"/>
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>3.7.4</t>
+        </is>
+      </c>
+      <c r="B127" t="n">
+        <v>3</v>
+      </c>
+      <c r="C127" t="inlineStr"/>
+      <c r="D127" t="inlineStr"/>
+      <c r="E127" s="5" t="inlineStr">
+        <is>
+          <t>Diesel Pump</t>
+        </is>
+      </c>
+      <c r="F127" t="n">
+        <v>4</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>5.1.4</t>
-        </is>
-      </c>
-      <c r="B128" t="n">
-        <v>3</v>
-      </c>
-      <c r="C128" t="inlineStr"/>
-      <c r="D128" t="inlineStr"/>
-      <c r="E128" s="5" t="inlineStr">
-        <is>
-          <t>Timbangan Laboratorium</t>
-        </is>
-      </c>
-      <c r="F128" t="n">
-        <v>1</v>
-      </c>
-      <c r="G128" t="n">
-        <v>0</v>
-      </c>
+      <c r="A128" s="3" t="inlineStr">
+        <is>
+          <t>3.8</t>
+        </is>
+      </c>
+      <c r="B128" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C128" s="3" t="inlineStr"/>
+      <c r="D128" s="4" t="inlineStr">
+        <is>
+          <t>Perkakas dan Alat Ukur Workshop</t>
+        </is>
+      </c>
+      <c r="E128" s="3" t="inlineStr"/>
+      <c r="F128" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G128" s="3" t="inlineStr"/>
     </row>
     <row r="129">
-      <c r="A129" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="B129" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C129" s="2" t="inlineStr">
-        <is>
-          <t>Gas Handling Tanur Reverberatory</t>
-        </is>
-      </c>
-      <c r="D129" s="2" t="inlineStr"/>
-      <c r="E129" s="2" t="inlineStr"/>
-      <c r="F129" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="G129" s="2" t="inlineStr"/>
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>3.8.2</t>
+        </is>
+      </c>
+      <c r="B129" t="n">
+        <v>3</v>
+      </c>
+      <c r="C129" t="inlineStr"/>
+      <c r="D129" t="inlineStr"/>
+      <c r="E129" s="5" t="inlineStr">
+        <is>
+          <t>Alat Ukur Maintenance / Peralatan Kelistrikan Workshop</t>
+        </is>
+      </c>
+      <c r="F129" t="n">
+        <v>1</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="130">
-      <c r="A130" s="3" t="inlineStr">
-        <is>
-          <t>7.1</t>
-        </is>
-      </c>
-      <c r="B130" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="C130" s="3" t="inlineStr"/>
-      <c r="D130" s="4" t="inlineStr">
-        <is>
-          <t>Gas Handling Tanur Reverb</t>
-        </is>
-      </c>
-      <c r="E130" s="3" t="inlineStr"/>
-      <c r="F130" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="G130" s="3" t="inlineStr"/>
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>Area Peleburan Sekunder / Dust Recovery</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr"/>
+      <c r="E130" s="2" t="inlineStr"/>
+      <c r="F130" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="G130" s="2" t="inlineStr"/>
     </row>
     <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>7.1.1</t>
-        </is>
-      </c>
-      <c r="B131" t="n">
-        <v>3</v>
-      </c>
-      <c r="C131" t="inlineStr"/>
-      <c r="D131" t="inlineStr"/>
-      <c r="E131" s="5" t="inlineStr">
-        <is>
-          <t>Skin Cooler - DCS Tanur Reverb</t>
-        </is>
-      </c>
-      <c r="F131" t="n">
-        <v>2</v>
-      </c>
-      <c r="G131" t="n">
-        <v>0</v>
-      </c>
+      <c r="A131" s="3" t="inlineStr">
+        <is>
+          <t>4.1</t>
+        </is>
+      </c>
+      <c r="B131" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C131" s="3" t="inlineStr"/>
+      <c r="D131" s="4" t="inlineStr">
+        <is>
+          <t>Sistem Penerimaan, Penyimpanan, dan Pelletizing</t>
+        </is>
+      </c>
+      <c r="E131" s="3" t="inlineStr"/>
+      <c r="F131" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="G131" s="3" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>7.1.2</t>
+          <t>4.1.3</t>
         </is>
       </c>
       <c r="B132" t="n">
@@ -3412,43 +3428,41 @@
       <c r="D132" t="inlineStr"/>
       <c r="E132" s="5" t="inlineStr">
         <is>
-          <t>Bag Filter - DCS Tanur Reverb</t>
+          <t>Pelletizer</t>
         </is>
       </c>
       <c r="F132" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G132" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>7.1.3</t>
-        </is>
-      </c>
-      <c r="B133" t="n">
-        <v>3</v>
-      </c>
-      <c r="C133" t="inlineStr"/>
-      <c r="D133" t="inlineStr"/>
-      <c r="E133" s="5" t="inlineStr">
-        <is>
-          <t>ID Fan - DCS Tanur Reverb</t>
-        </is>
-      </c>
-      <c r="F133" t="n">
-        <v>2</v>
-      </c>
-      <c r="G133" t="n">
-        <v>0</v>
-      </c>
+      <c r="A133" s="3" t="inlineStr">
+        <is>
+          <t>4.2</t>
+        </is>
+      </c>
+      <c r="B133" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C133" s="3" t="inlineStr"/>
+      <c r="D133" s="4" t="inlineStr">
+        <is>
+          <t>Rotary Kiln</t>
+        </is>
+      </c>
+      <c r="E133" s="3" t="inlineStr"/>
+      <c r="F133" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G133" s="3" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>7.1.4</t>
+          <t>4.2.2</t>
         </is>
       </c>
       <c r="B134" t="n">
@@ -3458,41 +3472,43 @@
       <c r="D134" t="inlineStr"/>
       <c r="E134" s="5" t="inlineStr">
         <is>
-          <t>Cerobong - DCS Tanur Reverb</t>
+          <t>Burner – Rotary Kiln</t>
         </is>
       </c>
       <c r="F134" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G134" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="B135" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C135" s="2" t="inlineStr">
-        <is>
-          <t>Area Kompresor / Udara Bertekanan</t>
-        </is>
-      </c>
-      <c r="D135" s="2" t="inlineStr"/>
-      <c r="E135" s="2" t="inlineStr"/>
-      <c r="F135" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G135" s="2" t="inlineStr"/>
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>4.2.3</t>
+        </is>
+      </c>
+      <c r="B135" t="n">
+        <v>3</v>
+      </c>
+      <c r="C135" t="inlineStr"/>
+      <c r="D135" t="inlineStr"/>
+      <c r="E135" s="5" t="inlineStr">
+        <is>
+          <t>Motor Gearbox</t>
+        </is>
+      </c>
+      <c r="F135" t="n">
+        <v>1</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="3" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="B136" s="3" t="n">
@@ -3501,19 +3517,19 @@
       <c r="C136" s="3" t="inlineStr"/>
       <c r="D136" s="4" t="inlineStr">
         <is>
-          <t>Kompressor</t>
+          <t>Sistem Flame Oven</t>
         </is>
       </c>
       <c r="E136" s="3" t="inlineStr"/>
       <c r="F136" s="3" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G136" s="3" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>8.1.2</t>
+          <t>4.3.1</t>
         </is>
       </c>
       <c r="B137" t="n">
@@ -3523,62 +3539,64 @@
       <c r="D137" t="inlineStr"/>
       <c r="E137" s="5" t="inlineStr">
         <is>
-          <t>Distribution Board</t>
+          <t>Tanur Flame Oven</t>
         </is>
       </c>
       <c r="F137" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G137" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="B138" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C138" s="2" t="inlineStr">
-        <is>
-          <t>Gas Handling dan Utilitas Penunjang (Registrasi Lapangan)</t>
-        </is>
-      </c>
-      <c r="D138" s="2" t="inlineStr"/>
-      <c r="E138" s="2" t="inlineStr"/>
-      <c r="F138" s="2" t="n">
-        <v>110</v>
-      </c>
-      <c r="G138" s="2" t="inlineStr"/>
+      <c r="A138" s="3" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
+      </c>
+      <c r="B138" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C138" s="3" t="inlineStr"/>
+      <c r="D138" s="4" t="inlineStr">
+        <is>
+          <t>Sistem Penanganan Gas Buang dan Debu</t>
+        </is>
+      </c>
+      <c r="E138" s="3" t="inlineStr"/>
+      <c r="F138" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="G138" s="3" t="inlineStr"/>
     </row>
     <row r="139">
-      <c r="A139" s="3" t="inlineStr">
-        <is>
-          <t>9.1</t>
-        </is>
-      </c>
-      <c r="B139" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="C139" s="3" t="inlineStr"/>
-      <c r="D139" s="4" t="inlineStr">
-        <is>
-          <t>Peralatan Penunjang (Registrasi Lapangan)</t>
-        </is>
-      </c>
-      <c r="E139" s="3" t="inlineStr"/>
-      <c r="F139" s="3" t="n">
-        <v>25</v>
-      </c>
-      <c r="G139" s="3" t="inlineStr"/>
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>4.4.1</t>
+        </is>
+      </c>
+      <c r="B139" t="n">
+        <v>3</v>
+      </c>
+      <c r="C139" t="inlineStr"/>
+      <c r="D139" t="inlineStr"/>
+      <c r="E139" s="5" t="inlineStr">
+        <is>
+          <t>Seattle Bawah Tanur</t>
+        </is>
+      </c>
+      <c r="F139" t="n">
+        <v>3</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>9.1.1</t>
+          <t>4.4.3</t>
         </is>
       </c>
       <c r="B140" t="n">
@@ -3588,43 +3606,41 @@
       <c r="D140" t="inlineStr"/>
       <c r="E140" s="5" t="inlineStr">
         <is>
-          <t>Water / Hydrant</t>
+          <t>Dust Collector</t>
         </is>
       </c>
       <c r="F140" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G140" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>9.1.2</t>
-        </is>
-      </c>
-      <c r="B141" t="n">
-        <v>3</v>
-      </c>
-      <c r="C141" t="inlineStr"/>
-      <c r="D141" t="inlineStr"/>
-      <c r="E141" s="5" t="inlineStr">
-        <is>
-          <t>Water Circulation</t>
-        </is>
-      </c>
-      <c r="F141" t="n">
-        <v>6</v>
-      </c>
-      <c r="G141" t="n">
-        <v>2</v>
-      </c>
+      <c r="A141" s="3" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="B141" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C141" s="3" t="inlineStr"/>
+      <c r="D141" s="4" t="inlineStr">
+        <is>
+          <t>Sistem Kelistrikan, Kontrol, Instrumentasi, dan Interlock</t>
+        </is>
+      </c>
+      <c r="E141" s="3" t="inlineStr"/>
+      <c r="F141" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G141" s="3" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>9.1.3</t>
+          <t>4.5.1</t>
         </is>
       </c>
       <c r="B142" t="n">
@@ -3634,66 +3650,62 @@
       <c r="D142" t="inlineStr"/>
       <c r="E142" s="5" t="inlineStr">
         <is>
-          <t>Trafo Step Up 20 kV</t>
+          <t>Panel Electrical</t>
         </is>
       </c>
       <c r="F142" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G142" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>9.1.4</t>
-        </is>
-      </c>
-      <c r="B143" t="n">
-        <v>3</v>
-      </c>
-      <c r="C143" t="inlineStr"/>
-      <c r="D143" t="inlineStr"/>
-      <c r="E143" s="5" t="inlineStr">
-        <is>
-          <t>Pneumatic System</t>
-        </is>
-      </c>
-      <c r="F143" t="n">
-        <v>2</v>
-      </c>
-      <c r="G143" t="n">
-        <v>1</v>
-      </c>
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>Area QC</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr"/>
+      <c r="E143" s="2" t="inlineStr"/>
+      <c r="F143" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G143" s="2" t="inlineStr"/>
     </row>
     <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>9.1.6</t>
-        </is>
-      </c>
-      <c r="B144" t="n">
-        <v>3</v>
-      </c>
-      <c r="C144" t="inlineStr"/>
-      <c r="D144" t="inlineStr"/>
-      <c r="E144" s="5" t="inlineStr">
-        <is>
-          <t>Motor Screw Hopper Elektroda Tanur</t>
-        </is>
-      </c>
-      <c r="F144" t="n">
-        <v>5</v>
-      </c>
-      <c r="G144" t="n">
-        <v>0</v>
-      </c>
+      <c r="A144" s="3" t="inlineStr">
+        <is>
+          <t>5.1</t>
+        </is>
+      </c>
+      <c r="B144" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C144" s="3" t="inlineStr"/>
+      <c r="D144" s="4" t="inlineStr">
+        <is>
+          <t>Lab. Analisis</t>
+        </is>
+      </c>
+      <c r="E144" s="3" t="inlineStr"/>
+      <c r="F144" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G144" s="3" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>9.1.7</t>
+          <t>5.1.4</t>
         </is>
       </c>
       <c r="B145" t="n">
@@ -3703,7 +3715,7 @@
       <c r="D145" t="inlineStr"/>
       <c r="E145" s="5" t="inlineStr">
         <is>
-          <t>Motor Pump Hydrant</t>
+          <t>Timbangan Laboratorium</t>
         </is>
       </c>
       <c r="F145" t="n">
@@ -3714,55 +3726,51 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>9.1.8</t>
-        </is>
-      </c>
-      <c r="B146" t="n">
-        <v>3</v>
-      </c>
-      <c r="C146" t="inlineStr"/>
-      <c r="D146" t="inlineStr"/>
-      <c r="E146" s="5" t="inlineStr">
-        <is>
-          <t>Motor Gearbox</t>
-        </is>
-      </c>
-      <c r="F146" t="n">
-        <v>1</v>
-      </c>
-      <c r="G146" t="n">
-        <v>0</v>
-      </c>
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>Gas Handling Tanur Reverberatory</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr"/>
+      <c r="E146" s="2" t="inlineStr"/>
+      <c r="F146" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="G146" s="2" t="inlineStr"/>
     </row>
     <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>9.1.9</t>
-        </is>
-      </c>
-      <c r="B147" t="n">
-        <v>3</v>
-      </c>
-      <c r="C147" t="inlineStr"/>
-      <c r="D147" t="inlineStr"/>
-      <c r="E147" s="5" t="inlineStr">
-        <is>
-          <t>Ruang Trafo</t>
-        </is>
-      </c>
-      <c r="F147" t="n">
-        <v>1</v>
-      </c>
-      <c r="G147" t="n">
-        <v>0</v>
-      </c>
+      <c r="A147" s="3" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="B147" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C147" s="3" t="inlineStr"/>
+      <c r="D147" s="4" t="inlineStr">
+        <is>
+          <t>Gas Handling Tanur Reverb</t>
+        </is>
+      </c>
+      <c r="E147" s="3" t="inlineStr"/>
+      <c r="F147" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="G147" s="3" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>9.1.10</t>
+          <t>7.1.1</t>
         </is>
       </c>
       <c r="B148" t="n">
@@ -3772,11 +3780,11 @@
       <c r="D148" t="inlineStr"/>
       <c r="E148" s="5" t="inlineStr">
         <is>
-          <t>Diesel Pump</t>
+          <t>Skin Cooler - DCS Tanur Reverb</t>
         </is>
       </c>
       <c r="F148" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G148" t="n">
         <v>0</v>
@@ -3785,7 +3793,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>9.1.11</t>
+          <t>7.1.2</t>
         </is>
       </c>
       <c r="B149" t="n">
@@ -3795,11 +3803,11 @@
       <c r="D149" t="inlineStr"/>
       <c r="E149" s="5" t="inlineStr">
         <is>
-          <t>Gudang Kapur</t>
+          <t>Bag Filter - DCS Tanur Reverb</t>
         </is>
       </c>
       <c r="F149" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G149" t="n">
         <v>0</v>
@@ -3808,7 +3816,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>9.1.13</t>
+          <t>7.1.3</t>
         </is>
       </c>
       <c r="B150" t="n">
@@ -3818,108 +3826,108 @@
       <c r="D150" t="inlineStr"/>
       <c r="E150" s="5" t="inlineStr">
         <is>
-          <t>Gudang LB3</t>
+          <t>ID Fan - DCS Tanur Reverb</t>
         </is>
       </c>
       <c r="F150" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G150" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="3" t="inlineStr">
-        <is>
-          <t>9.2</t>
-        </is>
-      </c>
-      <c r="B151" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="C151" s="3" t="inlineStr"/>
-      <c r="D151" s="4" t="inlineStr">
-        <is>
-          <t>Sistem Gas Handling, Ventilasi, dan Dust Collection</t>
-        </is>
-      </c>
-      <c r="E151" s="3" t="inlineStr"/>
-      <c r="F151" s="3" t="n">
-        <v>78</v>
-      </c>
-      <c r="G151" s="3" t="inlineStr"/>
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>7.1.4</t>
+        </is>
+      </c>
+      <c r="B151" t="n">
+        <v>3</v>
+      </c>
+      <c r="C151" t="inlineStr"/>
+      <c r="D151" t="inlineStr"/>
+      <c r="E151" s="5" t="inlineStr">
+        <is>
+          <t>Cerobong - DCS Tanur Reverb</t>
+        </is>
+      </c>
+      <c r="F151" t="n">
+        <v>2</v>
+      </c>
+      <c r="G151" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>9.2.1</t>
-        </is>
-      </c>
-      <c r="B152" t="n">
-        <v>3</v>
-      </c>
-      <c r="C152" t="inlineStr"/>
-      <c r="D152" t="inlineStr"/>
-      <c r="E152" s="5" t="inlineStr">
-        <is>
-          <t>ID Fan</t>
-        </is>
-      </c>
-      <c r="F152" t="n">
-        <v>34</v>
-      </c>
-      <c r="G152" t="n">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>Area dan Bangunan Umum</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr"/>
+      <c r="E152" s="2" t="inlineStr"/>
+      <c r="F152" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G152" s="2" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" s="3" t="inlineStr">
+        <is>
+          <t>8.1</t>
+        </is>
+      </c>
+      <c r="B153" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C153" s="3" t="inlineStr"/>
+      <c r="D153" s="4" t="inlineStr">
+        <is>
+          <t>Bangunan</t>
+        </is>
+      </c>
+      <c r="E153" s="3" t="inlineStr"/>
+      <c r="F153" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="G153" s="3" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>8.1.1</t>
+        </is>
+      </c>
+      <c r="B154" t="n">
+        <v>3</v>
+      </c>
+      <c r="C154" t="inlineStr"/>
+      <c r="D154" t="inlineStr"/>
+      <c r="E154" s="5" t="inlineStr">
+        <is>
+          <t>Pos Jaga / Area Genset</t>
+        </is>
+      </c>
+      <c r="F154" t="n">
         <v>4</v>
       </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>9.2.3</t>
-        </is>
-      </c>
-      <c r="B153" t="n">
-        <v>3</v>
-      </c>
-      <c r="C153" t="inlineStr"/>
-      <c r="D153" t="inlineStr"/>
-      <c r="E153" s="5" t="inlineStr">
-        <is>
-          <t>Exhaust Fan</t>
-        </is>
-      </c>
-      <c r="F153" t="n">
-        <v>44</v>
-      </c>
-      <c r="G153" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" s="3" t="inlineStr">
-        <is>
-          <t>9.3</t>
-        </is>
-      </c>
-      <c r="B154" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="C154" s="3" t="inlineStr"/>
-      <c r="D154" s="4" t="inlineStr">
-        <is>
-          <t>Kompresor dan Hydrant</t>
-        </is>
-      </c>
-      <c r="E154" s="3" t="inlineStr"/>
-      <c r="F154" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="G154" s="3" t="inlineStr"/>
+      <c r="G154" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>9.3.1</t>
+          <t>8.1.2</t>
         </is>
       </c>
       <c r="B155" t="n">
@@ -3929,43 +3937,41 @@
       <c r="D155" t="inlineStr"/>
       <c r="E155" s="5" t="inlineStr">
         <is>
-          <t>Jockey Pump</t>
+          <t>Area Peleburan / Tanur</t>
         </is>
       </c>
       <c r="F155" t="n">
         <v>1</v>
       </c>
       <c r="G155" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>9.3.2</t>
-        </is>
-      </c>
-      <c r="B156" t="n">
-        <v>3</v>
-      </c>
-      <c r="C156" t="inlineStr"/>
-      <c r="D156" t="inlineStr"/>
-      <c r="E156" s="5" t="inlineStr">
-        <is>
-          <t>Mesin Compressor Sullair</t>
-        </is>
-      </c>
-      <c r="F156" t="n">
-        <v>2</v>
-      </c>
-      <c r="G156" t="n">
-        <v>0</v>
-      </c>
+      <c r="A156" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>Bangunan dan Gedung Pabrik</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr"/>
+      <c r="E156" s="2" t="inlineStr"/>
+      <c r="F156" s="2" t="n">
+        <v>43</v>
+      </c>
+      <c r="G156" s="2" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" s="3" t="inlineStr">
         <is>
-          <t>9.4</t>
+          <t>9.1</t>
         </is>
       </c>
       <c r="B157" s="3" t="n">
@@ -3974,19 +3980,19 @@
       <c r="C157" s="3" t="inlineStr"/>
       <c r="D157" s="4" t="inlineStr">
         <is>
-          <t>Cooling System</t>
+          <t>Bangunan</t>
         </is>
       </c>
       <c r="E157" s="3" t="inlineStr"/>
       <c r="F157" s="3" t="n">
-        <v>2</v>
+        <v>43</v>
       </c>
       <c r="G157" s="3" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>9.4.1</t>
+          <t>9.1.1</t>
         </is>
       </c>
       <c r="B158" t="n">
@@ -3996,41 +4002,43 @@
       <c r="D158" t="inlineStr"/>
       <c r="E158" s="5" t="inlineStr">
         <is>
-          <t>Water Instalasi</t>
+          <t>Blower Vacuum</t>
         </is>
       </c>
       <c r="F158" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G158" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="3" t="inlineStr">
-        <is>
-          <t>9.9</t>
-        </is>
-      </c>
-      <c r="B159" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="C159" s="3" t="inlineStr"/>
-      <c r="D159" s="4" t="inlineStr">
-        <is>
-          <t>Panel Furnace Tegangan Rendah</t>
-        </is>
-      </c>
-      <c r="E159" s="3" t="inlineStr"/>
-      <c r="F159" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="G159" s="3" t="inlineStr"/>
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>9.1.2</t>
+        </is>
+      </c>
+      <c r="B159" t="n">
+        <v>3</v>
+      </c>
+      <c r="C159" t="inlineStr"/>
+      <c r="D159" t="inlineStr"/>
+      <c r="E159" s="5" t="inlineStr">
+        <is>
+          <t>Bangunan Crusher</t>
+        </is>
+      </c>
+      <c r="F159" t="n">
+        <v>1</v>
+      </c>
+      <c r="G159" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>9.9.1</t>
+          <t>9.1.3</t>
         </is>
       </c>
       <c r="B160" t="n">
@@ -4040,7 +4048,7 @@
       <c r="D160" t="inlineStr"/>
       <c r="E160" s="5" t="inlineStr">
         <is>
-          <t>Panel Furnace Tegangan Rendah</t>
+          <t>Gedung Antrasit, Workshop, dan Gudang Pasir</t>
         </is>
       </c>
       <c r="F160" t="n">
@@ -4051,51 +4059,55 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="B161" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C161" s="2" t="inlineStr">
-        <is>
-          <t>Area dan Bangunan Umum</t>
-        </is>
-      </c>
-      <c r="D161" s="2" t="inlineStr"/>
-      <c r="E161" s="2" t="inlineStr"/>
-      <c r="F161" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="G161" s="2" t="inlineStr"/>
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>9.1.4</t>
+        </is>
+      </c>
+      <c r="B161" t="n">
+        <v>3</v>
+      </c>
+      <c r="C161" t="inlineStr"/>
+      <c r="D161" t="inlineStr"/>
+      <c r="E161" s="5" t="inlineStr">
+        <is>
+          <t>Area Bahan Bakar / Gedung HTS MS</t>
+        </is>
+      </c>
+      <c r="F161" t="n">
+        <v>3</v>
+      </c>
+      <c r="G161" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="162">
-      <c r="A162" s="3" t="inlineStr">
-        <is>
-          <t>11.1</t>
-        </is>
-      </c>
-      <c r="B162" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="C162" s="3" t="inlineStr"/>
-      <c r="D162" s="4" t="inlineStr">
-        <is>
-          <t>Bangunan</t>
-        </is>
-      </c>
-      <c r="E162" s="3" t="inlineStr"/>
-      <c r="F162" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="G162" s="3" t="inlineStr"/>
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>9.1.5</t>
+        </is>
+      </c>
+      <c r="B162" t="n">
+        <v>3</v>
+      </c>
+      <c r="C162" t="inlineStr"/>
+      <c r="D162" t="inlineStr"/>
+      <c r="E162" s="5" t="inlineStr">
+        <is>
+          <t>Gedung Komposisi</t>
+        </is>
+      </c>
+      <c r="F162" t="n">
+        <v>1</v>
+      </c>
+      <c r="G162" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>11.1.1</t>
+          <t>9.1.6</t>
         </is>
       </c>
       <c r="B163" t="n">
@@ -4105,20 +4117,20 @@
       <c r="D163" t="inlineStr"/>
       <c r="E163" s="5" t="inlineStr">
         <is>
-          <t>Pos Jaga / Area Genset</t>
+          <t>Gedung Musholla</t>
         </is>
       </c>
       <c r="F163" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G163" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>11.1.2</t>
+          <t>9.1.7</t>
         </is>
       </c>
       <c r="B164" t="n">
@@ -4128,62 +4140,66 @@
       <c r="D164" t="inlineStr"/>
       <c r="E164" s="5" t="inlineStr">
         <is>
-          <t>Area Peleburan / Tanur</t>
+          <t>Gedung Office</t>
         </is>
       </c>
       <c r="F164" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G164" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="B165" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C165" s="2" t="inlineStr">
-        <is>
-          <t>Bangunan dan Gedung Pabrik</t>
-        </is>
-      </c>
-      <c r="D165" s="2" t="inlineStr"/>
-      <c r="E165" s="2" t="inlineStr"/>
-      <c r="F165" s="2" t="n">
-        <v>41</v>
-      </c>
-      <c r="G165" s="2" t="inlineStr"/>
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>9.1.8</t>
+        </is>
+      </c>
+      <c r="B165" t="n">
+        <v>3</v>
+      </c>
+      <c r="C165" t="inlineStr"/>
+      <c r="D165" t="inlineStr"/>
+      <c r="E165" s="5" t="inlineStr">
+        <is>
+          <t>Gedung Rotary Kiln &amp; Flame Oven</t>
+        </is>
+      </c>
+      <c r="F165" t="n">
+        <v>2</v>
+      </c>
+      <c r="G165" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="166">
-      <c r="A166" s="3" t="inlineStr">
-        <is>
-          <t>12.1</t>
-        </is>
-      </c>
-      <c r="B166" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="C166" s="3" t="inlineStr"/>
-      <c r="D166" s="4" t="inlineStr">
-        <is>
-          <t>Bangunan</t>
-        </is>
-      </c>
-      <c r="E166" s="3" t="inlineStr"/>
-      <c r="F166" s="3" t="n">
-        <v>41</v>
-      </c>
-      <c r="G166" s="3" t="inlineStr"/>
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>9.1.9</t>
+        </is>
+      </c>
+      <c r="B166" t="n">
+        <v>3</v>
+      </c>
+      <c r="C166" t="inlineStr"/>
+      <c r="D166" t="inlineStr"/>
+      <c r="E166" s="5" t="inlineStr">
+        <is>
+          <t>Gedung Timbangan</t>
+        </is>
+      </c>
+      <c r="F166" t="n">
+        <v>1</v>
+      </c>
+      <c r="G166" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>12.1.1</t>
+          <t>9.1.10</t>
         </is>
       </c>
       <c r="B167" t="n">
@@ -4193,11 +4209,11 @@
       <c r="D167" t="inlineStr"/>
       <c r="E167" s="5" t="inlineStr">
         <is>
-          <t>Blower Vacuum</t>
+          <t>Gudang Pasir</t>
         </is>
       </c>
       <c r="F167" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G167" t="n">
         <v>0</v>
@@ -4206,7 +4222,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>12.1.2</t>
+          <t>9.1.11</t>
         </is>
       </c>
       <c r="B168" t="n">
@@ -4216,20 +4232,20 @@
       <c r="D168" t="inlineStr"/>
       <c r="E168" s="5" t="inlineStr">
         <is>
-          <t>Bangunan Crusher</t>
+          <t>Gudang Sparepart</t>
         </is>
       </c>
       <c r="F168" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G168" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>12.1.3</t>
+          <t>9.1.12</t>
         </is>
       </c>
       <c r="B169" t="n">
@@ -4239,7 +4255,7 @@
       <c r="D169" t="inlineStr"/>
       <c r="E169" s="5" t="inlineStr">
         <is>
-          <t>Gedung Antrasit, Workshop, dan Gudang Pasir</t>
+          <t>Laboratorium</t>
         </is>
       </c>
       <c r="F169" t="n">
@@ -4252,7 +4268,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>12.1.4</t>
+          <t>9.1.13</t>
         </is>
       </c>
       <c r="B170" t="n">
@@ -4262,20 +4278,20 @@
       <c r="D170" t="inlineStr"/>
       <c r="E170" s="5" t="inlineStr">
         <is>
-          <t>Area Bahan Bakar / Gedung HTS MS</t>
+          <t>Gedung Produksi</t>
         </is>
       </c>
       <c r="F170" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G170" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>12.1.5</t>
+          <t>9.1.14</t>
         </is>
       </c>
       <c r="B171" t="n">
@@ -4285,20 +4301,20 @@
       <c r="D171" t="inlineStr"/>
       <c r="E171" s="5" t="inlineStr">
         <is>
-          <t>Gedung Komposisi</t>
+          <t>Gedung Crystallizer</t>
         </is>
       </c>
       <c r="F171" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G171" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>12.1.6</t>
+          <t>9.1.15</t>
         </is>
       </c>
       <c r="B172" t="n">
@@ -4308,7 +4324,7 @@
       <c r="D172" t="inlineStr"/>
       <c r="E172" s="5" t="inlineStr">
         <is>
-          <t>Gedung Musholla</t>
+          <t>Gedung Ruang Pompa</t>
         </is>
       </c>
       <c r="F172" t="n">
@@ -4321,7 +4337,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>12.1.7</t>
+          <t>9.1.16</t>
         </is>
       </c>
       <c r="B173" t="n">
@@ -4331,11 +4347,11 @@
       <c r="D173" t="inlineStr"/>
       <c r="E173" s="5" t="inlineStr">
         <is>
-          <t>Gedung Office</t>
+          <t>Gudang Kapur</t>
         </is>
       </c>
       <c r="F173" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G173" t="n">
         <v>0</v>
@@ -4344,7 +4360,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>12.1.8</t>
+          <t>9.1.17</t>
         </is>
       </c>
       <c r="B174" t="n">
@@ -4354,66 +4370,62 @@
       <c r="D174" t="inlineStr"/>
       <c r="E174" s="5" t="inlineStr">
         <is>
-          <t>Gedung Rotary Kiln &amp; Flame Oven</t>
+          <t>Gudang LB3</t>
         </is>
       </c>
       <c r="F174" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G174" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="175">
-      <c r="A175" t="inlineStr">
-        <is>
-          <t>12.1.9</t>
-        </is>
-      </c>
-      <c r="B175" t="n">
-        <v>3</v>
-      </c>
-      <c r="C175" t="inlineStr"/>
-      <c r="D175" t="inlineStr"/>
-      <c r="E175" s="5" t="inlineStr">
-        <is>
-          <t>Gedung Timbangan</t>
-        </is>
-      </c>
-      <c r="F175" t="n">
-        <v>1</v>
-      </c>
-      <c r="G175" t="n">
-        <v>0</v>
-      </c>
+      <c r="A175" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B175" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>Bangunan Workshop dan Rumah Peralatan</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="inlineStr"/>
+      <c r="E175" s="2" t="inlineStr"/>
+      <c r="F175" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="G175" s="2" t="inlineStr"/>
     </row>
     <row r="176">
-      <c r="A176" t="inlineStr">
-        <is>
-          <t>12.1.10</t>
-        </is>
-      </c>
-      <c r="B176" t="n">
-        <v>3</v>
-      </c>
-      <c r="C176" t="inlineStr"/>
-      <c r="D176" t="inlineStr"/>
-      <c r="E176" s="5" t="inlineStr">
-        <is>
-          <t>Gudang Pasir</t>
-        </is>
-      </c>
-      <c r="F176" t="n">
-        <v>4</v>
-      </c>
-      <c r="G176" t="n">
-        <v>0</v>
-      </c>
+      <c r="A176" s="3" t="inlineStr">
+        <is>
+          <t>10.1</t>
+        </is>
+      </c>
+      <c r="B176" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C176" s="3" t="inlineStr"/>
+      <c r="D176" s="4" t="inlineStr">
+        <is>
+          <t>Bangunan</t>
+        </is>
+      </c>
+      <c r="E176" s="3" t="inlineStr"/>
+      <c r="F176" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="G176" s="3" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>12.1.11</t>
+          <t>10.1.1</t>
         </is>
       </c>
       <c r="B177" t="n">
@@ -4423,11 +4435,11 @@
       <c r="D177" t="inlineStr"/>
       <c r="E177" s="5" t="inlineStr">
         <is>
-          <t>Gudang Sparepart</t>
+          <t>Workshop Teknik</t>
         </is>
       </c>
       <c r="F177" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G177" t="n">
         <v>1</v>
@@ -4436,7 +4448,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>12.1.12</t>
+          <t>10.1.2</t>
         </is>
       </c>
       <c r="B178" t="n">
@@ -4446,11 +4458,11 @@
       <c r="D178" t="inlineStr"/>
       <c r="E178" s="5" t="inlineStr">
         <is>
-          <t>Laboratorium</t>
+          <t>Rumah Parkir Alat Berat</t>
         </is>
       </c>
       <c r="F178" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G178" t="n">
         <v>0</v>
@@ -4459,7 +4471,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>12.1.13</t>
+          <t>10.1.3</t>
         </is>
       </c>
       <c r="B179" t="n">
@@ -4469,20 +4481,20 @@
       <c r="D179" t="inlineStr"/>
       <c r="E179" s="5" t="inlineStr">
         <is>
-          <t>Gedung Produksi</t>
+          <t>Workshop Tanur Listrik</t>
         </is>
       </c>
       <c r="F179" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G179" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>12.1.14</t>
+          <t>10.1.4</t>
         </is>
       </c>
       <c r="B180" t="n">
@@ -4492,11 +4504,11 @@
       <c r="D180" t="inlineStr"/>
       <c r="E180" s="5" t="inlineStr">
         <is>
-          <t>Gedung Crystallizer</t>
+          <t>Rumah Kompresor</t>
         </is>
       </c>
       <c r="F180" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G180" t="n">
         <v>1</v>
@@ -4505,7 +4517,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>12.1.15</t>
+          <t>10.1.5</t>
         </is>
       </c>
       <c r="B181" t="n">
@@ -4515,7 +4527,7 @@
       <c r="D181" t="inlineStr"/>
       <c r="E181" s="5" t="inlineStr">
         <is>
-          <t>Gedung Ruang Pompa</t>
+          <t>Rumah Cooling System</t>
         </is>
       </c>
       <c r="F181" t="n">
@@ -4526,97 +4538,97 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="B182" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C182" s="2" t="inlineStr">
-        <is>
-          <t>Bangunan Workshop dan Rumah Peralatan</t>
-        </is>
-      </c>
-      <c r="D182" s="2" t="inlineStr"/>
-      <c r="E182" s="2" t="inlineStr"/>
-      <c r="F182" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="G182" s="2" t="inlineStr"/>
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>10.1.6</t>
+        </is>
+      </c>
+      <c r="B182" t="n">
+        <v>3</v>
+      </c>
+      <c r="C182" t="inlineStr"/>
+      <c r="D182" t="inlineStr"/>
+      <c r="E182" s="5" t="inlineStr">
+        <is>
+          <t>Workshop Listrik</t>
+        </is>
+      </c>
+      <c r="F182" t="n">
+        <v>1</v>
+      </c>
+      <c r="G182" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="183">
-      <c r="A183" s="3" t="inlineStr">
-        <is>
-          <t>13.1</t>
-        </is>
-      </c>
-      <c r="B183" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="C183" s="3" t="inlineStr"/>
-      <c r="D183" s="4" t="inlineStr">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>10.1.8</t>
+        </is>
+      </c>
+      <c r="B183" t="n">
+        <v>3</v>
+      </c>
+      <c r="C183" t="inlineStr"/>
+      <c r="D183" t="inlineStr"/>
+      <c r="E183" s="5" t="inlineStr">
+        <is>
+          <t>Rumah Baghouse</t>
+        </is>
+      </c>
+      <c r="F183" t="n">
+        <v>3</v>
+      </c>
+      <c r="G183" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B184" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C184" s="2" t="inlineStr">
+        <is>
+          <t>Struktur dan Bangunan Tanur / Pemurnian</t>
+        </is>
+      </c>
+      <c r="D184" s="2" t="inlineStr"/>
+      <c r="E184" s="2" t="inlineStr"/>
+      <c r="F184" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="G184" s="2" t="inlineStr"/>
+    </row>
+    <row r="185">
+      <c r="A185" s="3" t="inlineStr">
+        <is>
+          <t>11.1</t>
+        </is>
+      </c>
+      <c r="B185" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C185" s="3" t="inlineStr"/>
+      <c r="D185" s="4" t="inlineStr">
         <is>
           <t>Bangunan</t>
         </is>
       </c>
-      <c r="E183" s="3" t="inlineStr"/>
-      <c r="F183" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="G183" s="3" t="inlineStr"/>
-    </row>
-    <row r="184">
-      <c r="A184" t="inlineStr">
-        <is>
-          <t>13.1.1</t>
-        </is>
-      </c>
-      <c r="B184" t="n">
-        <v>3</v>
-      </c>
-      <c r="C184" t="inlineStr"/>
-      <c r="D184" t="inlineStr"/>
-      <c r="E184" s="5" t="inlineStr">
-        <is>
-          <t>Workshop Teknik</t>
-        </is>
-      </c>
-      <c r="F184" t="n">
-        <v>4</v>
-      </c>
-      <c r="G184" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" t="inlineStr">
-        <is>
-          <t>13.1.2</t>
-        </is>
-      </c>
-      <c r="B185" t="n">
-        <v>3</v>
-      </c>
-      <c r="C185" t="inlineStr"/>
-      <c r="D185" t="inlineStr"/>
-      <c r="E185" s="5" t="inlineStr">
-        <is>
-          <t>Rumah Parkir Alat Berat</t>
-        </is>
-      </c>
-      <c r="F185" t="n">
-        <v>1</v>
-      </c>
-      <c r="G185" t="n">
-        <v>0</v>
-      </c>
+      <c r="E185" s="3" t="inlineStr"/>
+      <c r="F185" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="G185" s="3" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>13.1.3</t>
+          <t>11.1.1</t>
         </is>
       </c>
       <c r="B186" t="n">
@@ -4626,11 +4638,11 @@
       <c r="D186" t="inlineStr"/>
       <c r="E186" s="5" t="inlineStr">
         <is>
-          <t>Workshop Tanur Listrik</t>
+          <t>Rumah Mainflue</t>
         </is>
       </c>
       <c r="F186" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G186" t="n">
         <v>0</v>
@@ -4639,7 +4651,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>13.1.4</t>
+          <t>11.1.2</t>
         </is>
       </c>
       <c r="B187" t="n">
@@ -4649,20 +4661,20 @@
       <c r="D187" t="inlineStr"/>
       <c r="E187" s="5" t="inlineStr">
         <is>
-          <t>Rumah Kompresor</t>
+          <t>Struktur Fixed Tanur</t>
         </is>
       </c>
       <c r="F187" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G187" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>13.1.5</t>
+          <t>11.1.3</t>
         </is>
       </c>
       <c r="B188" t="n">
@@ -4672,11 +4684,11 @@
       <c r="D188" t="inlineStr"/>
       <c r="E188" s="5" t="inlineStr">
         <is>
-          <t>Rumah Cooling System</t>
+          <t>Struktur Fixed Pemurnian</t>
         </is>
       </c>
       <c r="F188" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G188" t="n">
         <v>0</v>
@@ -4685,7 +4697,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>13.1.6</t>
+          <t>11.1.4</t>
         </is>
       </c>
       <c r="B189" t="n">
@@ -4695,7 +4707,7 @@
       <c r="D189" t="inlineStr"/>
       <c r="E189" s="5" t="inlineStr">
         <is>
-          <t>Workshop Listrik</t>
+          <t>Gedung Refining</t>
         </is>
       </c>
       <c r="F189" t="n">
@@ -4705,230 +4717,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="190">
-      <c r="A190" t="inlineStr">
-        <is>
-          <t>13.1.8</t>
-        </is>
-      </c>
-      <c r="B190" t="n">
-        <v>3</v>
-      </c>
-      <c r="C190" t="inlineStr"/>
-      <c r="D190" t="inlineStr"/>
-      <c r="E190" s="5" t="inlineStr">
-        <is>
-          <t>Rumah Baghouse</t>
-        </is>
-      </c>
-      <c r="F190" t="n">
-        <v>3</v>
-      </c>
-      <c r="G190" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="B191" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C191" s="2" t="inlineStr">
-        <is>
-          <t>Struktur dan Bangunan Tanur / Pemurnian</t>
-        </is>
-      </c>
-      <c r="D191" s="2" t="inlineStr"/>
-      <c r="E191" s="2" t="inlineStr"/>
-      <c r="F191" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="G191" s="2" t="inlineStr"/>
-    </row>
-    <row r="192">
-      <c r="A192" s="3" t="inlineStr">
-        <is>
-          <t>14.1</t>
-        </is>
-      </c>
-      <c r="B192" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="C192" s="3" t="inlineStr"/>
-      <c r="D192" s="4" t="inlineStr">
-        <is>
-          <t>Bangunan</t>
-        </is>
-      </c>
-      <c r="E192" s="3" t="inlineStr"/>
-      <c r="F192" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="G192" s="3" t="inlineStr"/>
-    </row>
-    <row r="193">
-      <c r="A193" t="inlineStr">
-        <is>
-          <t>14.1.1</t>
-        </is>
-      </c>
-      <c r="B193" t="n">
-        <v>3</v>
-      </c>
-      <c r="C193" t="inlineStr"/>
-      <c r="D193" t="inlineStr"/>
-      <c r="E193" s="5" t="inlineStr">
-        <is>
-          <t>Rumah Mainflue</t>
-        </is>
-      </c>
-      <c r="F193" t="n">
-        <v>5</v>
-      </c>
-      <c r="G193" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" t="inlineStr">
-        <is>
-          <t>14.1.2</t>
-        </is>
-      </c>
-      <c r="B194" t="n">
-        <v>3</v>
-      </c>
-      <c r="C194" t="inlineStr"/>
-      <c r="D194" t="inlineStr"/>
-      <c r="E194" s="5" t="inlineStr">
-        <is>
-          <t>Struktur Fixed Tanur</t>
-        </is>
-      </c>
-      <c r="F194" t="n">
-        <v>8</v>
-      </c>
-      <c r="G194" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" t="inlineStr">
-        <is>
-          <t>14.1.3</t>
-        </is>
-      </c>
-      <c r="B195" t="n">
-        <v>3</v>
-      </c>
-      <c r="C195" t="inlineStr"/>
-      <c r="D195" t="inlineStr"/>
-      <c r="E195" s="5" t="inlineStr">
-        <is>
-          <t>Struktur Fixed Pemurnian</t>
-        </is>
-      </c>
-      <c r="F195" t="n">
-        <v>2</v>
-      </c>
-      <c r="G195" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" t="inlineStr">
-        <is>
-          <t>14.1.4</t>
-        </is>
-      </c>
-      <c r="B196" t="n">
-        <v>3</v>
-      </c>
-      <c r="C196" t="inlineStr"/>
-      <c r="D196" t="inlineStr"/>
-      <c r="E196" s="5" t="inlineStr">
-        <is>
-          <t>Gedung Refining</t>
-        </is>
-      </c>
-      <c r="F196" t="n">
-        <v>1</v>
-      </c>
-      <c r="G196" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="B197" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C197" s="2" t="inlineStr">
-        <is>
-          <t>Area Genset dan Power House</t>
-        </is>
-      </c>
-      <c r="D197" s="2" t="inlineStr"/>
-      <c r="E197" s="2" t="inlineStr"/>
-      <c r="F197" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="G197" s="2" t="inlineStr"/>
-    </row>
-    <row r="198">
-      <c r="A198" s="3" t="inlineStr">
-        <is>
-          <t>16.1</t>
-        </is>
-      </c>
-      <c r="B198" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="C198" s="3" t="inlineStr"/>
-      <c r="D198" s="4" t="inlineStr">
-        <is>
-          <t>Genset dan Power House</t>
-        </is>
-      </c>
-      <c r="E198" s="3" t="inlineStr"/>
-      <c r="F198" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="G198" s="3" t="inlineStr"/>
-    </row>
-    <row r="199">
-      <c r="A199" t="inlineStr">
-        <is>
-          <t>16.1.1</t>
-        </is>
-      </c>
-      <c r="B199" t="n">
-        <v>3</v>
-      </c>
-      <c r="C199" t="inlineStr"/>
-      <c r="D199" t="inlineStr"/>
-      <c r="E199" s="5" t="inlineStr">
-        <is>
-          <t>Panel Battery</t>
-        </is>
-      </c>
-      <c r="F199" t="n">
-        <v>2</v>
-      </c>
-      <c r="G199" t="n">
-        <v>0</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:G199"/>
+  <autoFilter ref="A1:G189"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>